--- a/extra/report/No.課題4_テスト結果.xlsx
+++ b/extra/report/No.課題4_テスト結果.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0108BE1-1FAD-4A28-8351-F19E611F6FC9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED26FD92-8F59-4E49-8514-929C55534DC7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="10" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="前提" sheetId="2" r:id="rId1"/>
@@ -15,13 +15,23 @@
     <sheet name="ケース16-17" sheetId="5" r:id="rId5"/>
     <sheet name="ケース18-29" sheetId="6" r:id="rId6"/>
     <sheet name="ケース30-39" sheetId="7" r:id="rId7"/>
+    <sheet name="ケース40-41" sheetId="8" r:id="rId8"/>
+    <sheet name="ケース42" sheetId="9" r:id="rId9"/>
+    <sheet name="ケース43" sheetId="10" r:id="rId10"/>
+    <sheet name="ケース44-47" sheetId="11" r:id="rId11"/>
+    <sheet name="ケース48-49" sheetId="12" r:id="rId12"/>
+    <sheet name="ケース50" sheetId="13" r:id="rId13"/>
+    <sheet name="ケース51" sheetId="14" r:id="rId14"/>
+    <sheet name="ケース52-53" sheetId="15" r:id="rId15"/>
+    <sheet name="ケース54-57" sheetId="16" r:id="rId16"/>
+    <sheet name="ケース58-59" sheetId="17" r:id="rId17"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="84">
   <si>
     <t>【前提】</t>
     <rPh sb="1" eb="3">
@@ -103,10 +113,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>12.「料金名」に”月額料金”「月額料金」に”1000”「加入日」に”2025年8月19日”「解約日に」”2025年9月19日”を記載して保存ボタンを押下した時に、料金編集画面に遷移する</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>13.項目12を実行した後にデーターベースに「料金名」に”月額料金”「月額料金」に”1000”「加入日」に”2025年8月19日”「解約日」に”2025年9月19”日と記載された料金情報が存在することを確認</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -119,39 +125,6 @@
       <t>ハ</t>
     </rPh>
     <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>13のテスト結果</t>
-    <rPh sb="6" eb="8">
-      <t>ケッカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <t>料金新規追加画面の「解約日」だけ情報を記載</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="double"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>せず</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>に登録ボタン押下</t>
-    </r>
   </si>
   <si>
     <t>14.「料金名」に”月額料金”「月額料金」に”1000”「加入日」に”2025年8月20日”を記載して保存ボタンを押下した時に、料金編集画面に遷移する</t>
@@ -171,10 +144,6 @@
   </si>
   <si>
     <t>17.項目14を実行した後にデーターベースに全カラムになにも情報がないレコードが存在しないことを確認する</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>■</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -256,19 +225,11 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>34.料金番号”12”の料金情報に全て空欄で登録ボタンを押下したときに、「料金」「月額料金」「加入日」の欄の下に”この項目の入力は必須です。”と表示される</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>35.データーベースにある料金番号”12”のレコードが「料金名」が”通常”「月額料金」が”5000”「加入日」が”2025年8月18日”「解約日」が”2025年8月18日”のまま変更されていないことを確認する</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>36.キャンセルボタンを押下した時に料金情報検索画面に遷移する。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>37.料金番号“15”の料金情報編集画面で削除ボタンを押下した時に、ブラウザ上部に”id:4を削除してもよろしいですか？”と表示される</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -279,12 +240,247 @@
     <t>39.項目38を実行した後にデーターベースに料金番号”15”のレコードが存在しないことを確認する</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>■料金テーブルのカラムがわかるように張っておきます</t>
+    <rPh sb="1" eb="3">
+      <t>リョウキン</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ハ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34.料金番号”12”の料金情報に全て空欄で保存ボタンを押下したときに、「料金」「月額料金」「加入日」の欄の下に”この項目の入力は必須です。”と表示される</t>
+    <rPh sb="22" eb="24">
+      <t>ホゾン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>37.料金番号“15”の料金情報編集画面で削除ボタンを押下した時に、ブラウザ上部に”id:15を削除してもよろしいですか？”と表示される</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>料金編集画面で必須項目に情報を記載せずに保存ボタン押下</t>
+  </si>
+  <si>
+    <r>
+      <t>40.全て空欄で登録ボタンを押下したときに、「料金」「月額料金」「加入日」の欄の下に”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>この項目の入力は必須です。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>”と表示される</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>項目40を実行した後にデーターベースに全カラムになにも情報がないレコードが存在しないことを確認する</t>
+  </si>
+  <si>
+    <t>料金新規追加画面の料金名の入力チェック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>42.「料金名」が127文字までしか入力でないことを確認する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>料金新規追加画面の月額料金の入力チェック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>43.「月額料金」に”999999999”と入力し9文字までしか入力できないことを確認する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>料金新規追加画面の月額料金の境界値チェック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>44.「月額料金」に”-1”と入力して保存ボタンを押下した時に、” この項目は0以上の数値を入力してください。”と表示される</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>45.「料金名」:”月額料金”「月額料金」:”0”「加入日」:”2025/10/10”と記載して保存ボタンを押下した時に、警告文が表示されずバリデーションチェックに引っかからないことを確認する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>46.「料金名」:”月額料金”「月額料金」:”999999999”「加入日」:”2025/10/10”と記載して保存ボタンを押下した時に、警告文が表示されずバリデーションチェックに引っかからないことを確認する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>47.「月額料金」に”1000000000”と入力して保存ボタンを押下した時に、”この項目は999999999以下の数値を入力してください。”と表示される</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>料金新規追加画面で不正な値を入力して保存ボタンを押下</t>
+  </si>
+  <si>
+    <r>
+      <t>48.「月額料金」で数字以外を入力して保存ボタンを押下した時に、月額料金の欄の下に”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>不正な値が入力されています。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>”と表示される</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>49.項目46を実行した後にデーターベースの「月額料金」カラムに数字以外の値が入っているレコードが存在しないことを確認する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>料金編集画面の料金名の入力チェック</t>
+  </si>
+  <si>
+    <t>50.「料金名」が127文字までしか入力でないことを確認する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>料金新規追加画面の「解約日」だけ情報を記載</t>
+    </r>
+    <r>
+      <rPr>
+        <u val="double"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>せず</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>に登録ボタン押下</t>
+    </r>
+  </si>
+  <si>
+    <t>料金編集画面の月額料金の入力チェック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>51.「月額料金」に”999999999”と入力して9文字までしか入力できないことを確認する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>料金編集画面の月額料金のに数字以外の文字を入力</t>
+  </si>
+  <si>
+    <t>52.「月額料金」で数字以外を入力して保存ボタンを押下した時に、”不正な値が入力されています。”と表示される</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>53.項目50を実行した後にデーターベースの「月額料金」カラムに数字以外の値が入っているレコードが存在しないことを確認する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>12.「料金名」に”月額料金”「月額料金」に”2000”「加入日」に”2025年8月19日”「解約日に」”2025年9月19日”を記載して保存ボタンを押下した時に、料金編集画面に遷移する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>項目13のテスト結果</t>
+    <rPh sb="0" eb="2">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ケッカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>■詳細設計書</t>
+    <rPh sb="1" eb="6">
+      <t>ショウサイセッケイショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>54.「月額料金」に”-1”と入力して保存ボタンを押下した時に、” この項目は0以上の数値を入力してください。”と表示される</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>55.「料金名」に”月額料金”「月額料金」に”0”「加入日」に”2025年10月10日”と記載して保存ボタンを押下した時に警告文が表示されずバリデーションチェックに引っかからないことを確認する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>56.「料金名」に”月額料金”「月額料金」に”999999999”「加入日」に”2025/10/10”と記載して保存ボタンを押下した時に、警告文が表示されずバリデーションチェックに引っかからないことを確認する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>57.「月額料金」に”1000000000”と入力して保存ボタンを押下した時に、”この項目は999999999以下の数値を入力してください。”と表示される</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>料金編集画面の月額料金の境界値チェック</t>
+    <rPh sb="2" eb="4">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>料金編集画面で不正な値を入力する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>58.「月額料金」で数字以外を入力して保存ボタンを押下した時に、データーベースに情報が保存されないことを確認</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>59.項目58を実行した後にデーターベースの「月額料金」カラムに数字以外の値が入っているレコードが存在しないことを確認する</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -298,13 +494,6 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
@@ -329,12 +518,37 @@
       <family val="2"/>
     </font>
     <font>
-      <u val="double"/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u val="double"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="2">
@@ -357,12 +571,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -424,6 +640,3431 @@
         <a:xfrm>
           <a:off x="685800" y="1066800"/>
           <a:ext cx="10058400" cy="6558376"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>448120</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>60195</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9EF0966D-9E1D-4AC0-8F77-28E9E9F6FFC7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="870857"/>
+          <a:ext cx="3191320" cy="2324424"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>672286</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>13139</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>105679</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{119866D4-301D-4A43-8EAC-56BE8B89A69E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="672286" y="4112173"/>
+          <a:ext cx="2743576" cy="1800472"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>684608</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>172639</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>416718</xdr:colOff>
+      <xdr:row>130</xdr:row>
+      <xdr:rowOff>124941</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="47" name="図 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5580952D-1B52-48EE-8D1E-CB782D6723D7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="684608" y="20716873"/>
+          <a:ext cx="3155157" cy="1851349"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>5434</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>149087</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>32203</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="36" name="図 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3C98C44-D2DB-4441-A40F-A1EC6DFC880F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="692891" y="11628783"/>
+          <a:ext cx="2056935" cy="2840007"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>683172</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>184733</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>91110</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{070722C5-13E8-4D93-B81E-07CA6EE0C4B1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="683172" y="869675"/>
+          <a:ext cx="2251387" cy="3048000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>593271</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>119930</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>357539</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>81643</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="正方形/長方形 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C29E4D3C-A362-4859-9395-F383C7E8DFC1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1279071" y="3603359"/>
+          <a:ext cx="450068" cy="310055"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent2"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123967</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>155215</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>124810</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>52552</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="10" name="直線矢印コネクタ 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C052E4C8-7B92-4835-B3FF-63E59F647BEF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1490312" y="3912663"/>
+          <a:ext cx="843" cy="1092889"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>4317</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>162160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>39247</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="図 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9AA9333D-54A5-4BDD-97C1-8708F576CFF0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="690117" y="6606503"/>
+          <a:ext cx="1406530" cy="1906126"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>5444</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>174171</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>664030</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>11134</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="図 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD0CF1A9-7A31-42FE-BF26-78CCD288C985}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="691244" y="8708571"/>
+          <a:ext cx="1344386" cy="2275363"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>375556</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>143464</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>655451</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="正方形/長方形 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3121B426-A255-4EF9-9573-63F8EA7F8280}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1061356" y="8329521"/>
+          <a:ext cx="279895" cy="204880"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent2"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>503109</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>67442</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>511392</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>42595</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="19" name="直線矢印コネクタ 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FB111C0-97C7-4C92-9A3C-4A76C69E3DC3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="1188909" y="8601842"/>
+          <a:ext cx="8283" cy="1368524"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>571499</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>77390</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>303608</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>23812</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="正方形/長方形 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9AF2882B-2579-4D7B-8F10-463C30D3C2D4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1256108" y="14061281"/>
+          <a:ext cx="416719" cy="291703"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent2"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>5953</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>166687</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>684609</xdr:colOff>
+      <xdr:row>118</xdr:row>
+      <xdr:rowOff>105698</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="40" name="図 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D4296AC-6786-458E-863A-05D644620DB6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="690562" y="17776031"/>
+          <a:ext cx="2047875" cy="2701261"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>410766</xdr:colOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>152710</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>137440</xdr:colOff>
+      <xdr:row>118</xdr:row>
+      <xdr:rowOff>107156</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="41" name="正方形/長方形 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF55D36F-2785-472A-ADF4-FFAD89CF9D73}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1095375" y="20179023"/>
+          <a:ext cx="411284" cy="299727"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent2"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>26142</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>588065</xdr:colOff>
+      <xdr:row>127</xdr:row>
+      <xdr:rowOff>158664</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="43" name="直線矢印コネクタ 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9228A072-88A2-4CBD-A4BC-154FC0EC3E21}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="1256109" y="20570376"/>
+          <a:ext cx="16565" cy="1513647"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>62377</xdr:colOff>
+      <xdr:row>130</xdr:row>
+      <xdr:rowOff>98096</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>410766</xdr:colOff>
+      <xdr:row>130</xdr:row>
+      <xdr:rowOff>101203</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="45" name="直線コネクタ 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C49E3D8-DC6F-4012-B96D-572284F7461D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1431596" y="22541377"/>
+          <a:ext cx="2402217" cy="3107"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>6990</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>159181</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>11907</xdr:colOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>124293</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="49" name="図 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78D55993-0D19-4F75-AD22-1D5F2E8F0A53}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="691599" y="14660994"/>
+          <a:ext cx="2058746" cy="2554721"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>65484</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>77390</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="28" name="直線矢印コネクタ 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{462C3006-1E86-4000-93BD-597F7B5741FE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="1434703" y="14424422"/>
+          <a:ext cx="11906" cy="1381125"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>341586</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>98534</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>670034</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>98534</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="53" name="直線コネクタ 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A225DA1D-7B8C-4DF9-9BD9-CC72F3199426}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1707931" y="5905500"/>
+          <a:ext cx="1694793" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>684609</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>386198</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>144639</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02517A77-1B06-49B7-B08A-776148F6CDB8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="684609" y="863203"/>
+          <a:ext cx="3124636" cy="4115374"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>684609</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>567198</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>113535</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF247065-A858-47CF-856D-B8985C3C0448}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="684609" y="5179219"/>
+          <a:ext cx="3305636" cy="3048425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>255985</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>89297</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>172640</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>142874</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="正方形/長方形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7308C100-B0A8-41A4-A6A5-53ECA35E8A0A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="940594" y="4577953"/>
+          <a:ext cx="601265" cy="398859"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent2"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>511969</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>65484</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>535782</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>130969</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="8" name="直線矢印コネクタ 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE4D9B37-874D-46A3-A6E6-5777E7D5696A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="1196578" y="5072062"/>
+          <a:ext cx="23813" cy="1791891"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>11906</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>53578</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>517922</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>53578</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="12" name="直線コネクタ 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F03A796-5A33-41EF-A2DE-4984DD0C6699}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2065734" y="8167687"/>
+          <a:ext cx="1875235" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>5437</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>16565</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>53658</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="図 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16DEEE84-DBB5-4D42-A8F6-2A66B11A5529}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="691237" y="8760515"/>
+          <a:ext cx="4109363" cy="3294643"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>683172</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>672941</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>45983</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61B01C12-8549-44C3-96A9-0B5A6606137C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="683172" y="853966"/>
+          <a:ext cx="5455148" cy="1583120"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>22787</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>8210</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>101105</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>48427</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D73D182F-1869-4FB9-A940-527F08CB7F8B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="707396" y="2770460"/>
+          <a:ext cx="4870584" cy="1939264"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>11814</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>48153</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>388530</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>119062</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="吹き出し: 角を丸めた四角形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60DA0D21-A7BB-4E6A-9FA1-EE5DC320612D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3434861" y="1256637"/>
+          <a:ext cx="2430544" cy="588831"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -23853"/>
+            <a:gd name="adj2" fmla="val 81492"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="+mn-ea"/>
+              <a:ea typeface="+mn-ea"/>
+            </a:rPr>
+            <a:t>ステップ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="+mn-ea"/>
+              <a:ea typeface="+mn-ea"/>
+            </a:rPr>
+            <a:t>1.128</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="+mn-ea"/>
+              <a:ea typeface="+mn-ea"/>
+            </a:rPr>
+            <a:t>文字以上入力を試みてそれをコピーする</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>437247</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>97918</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>135075</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>62959</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="吹き出し: 角を丸めた四角形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C03E0F59-71D5-480D-B880-CE8749AE03E7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2491075" y="4241293"/>
+          <a:ext cx="2436266" cy="482963"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -66641"/>
+            <a:gd name="adj2" fmla="val 20075"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="+mn-ea"/>
+              <a:ea typeface="+mn-ea"/>
+            </a:rPr>
+            <a:t>ステップ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="+mn-ea"/>
+              <a:ea typeface="+mn-ea"/>
+            </a:rPr>
+            <a:t>2.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="+mn-ea"/>
+              <a:ea typeface="+mn-ea"/>
+            </a:rPr>
+            <a:t>メモ帳に張り付けて</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="+mn-ea"/>
+              <a:ea typeface="+mn-ea"/>
+            </a:rPr>
+            <a:t>127</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="+mn-ea"/>
+              <a:ea typeface="+mn-ea"/>
+            </a:rPr>
+            <a:t>文字までしか入力できないことを確認</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>448216</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>19563</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48AB80B0-B64E-4F17-8AD5-FBC879CFB416}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="870857"/>
+          <a:ext cx="3877216" cy="3677163"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>683172</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>666750</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>161248</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{512F4A59-2E8C-4882-8ACA-B25115D362E9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="683172" y="863204"/>
+          <a:ext cx="1352797" cy="2232935"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>386954</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>21323</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7077F7B1-4968-42E2-88AC-5F04ADB8DE67}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="684610" y="3280173"/>
+          <a:ext cx="1756172" cy="1575088"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>153329</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>88281</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>464634</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>134744</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="正方形/長方形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9DCB0A3-FDB1-4243-8EFC-019595A5D158}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="840988" y="2838915"/>
+          <a:ext cx="311305" cy="218378"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent2"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>283426</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>51110</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>288073</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>83634</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="8" name="直線矢印コネクタ 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A840CE5-628B-4176-9522-730C0186A2BA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="971085" y="3145573"/>
+          <a:ext cx="4647" cy="892098"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>46464</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>9292</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>367061</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>13939</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="10" name="直線コネクタ 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FA7DD84-9A2E-4D57-8F6F-990D69BA5299}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1421781" y="4822902"/>
+          <a:ext cx="1008256" cy="4647"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>684609</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>172640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>669487</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>148828</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="図 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2FA29F8-FA32-4026-BD41-763D07505C53}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="684609" y="5351859"/>
+          <a:ext cx="4092534" cy="3429000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>684609</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>262356</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>107701</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="33" name="図 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF101071-CD91-4E3B-BA53-28D44F812F2A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="684609" y="863203"/>
+          <a:ext cx="3000794" cy="3905795"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>5434</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>4887</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>642937</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>56826</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{736CB2D9-39B1-45BB-BEE5-7248CE18DE77}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="690043" y="5011465"/>
+          <a:ext cx="2691332" cy="1605705"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>381258</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>44001</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>248736</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>60567</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="正方形/長方形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65AD030E-7AC0-4D2A-8F21-D287159B0B78}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1750477" y="4360017"/>
+          <a:ext cx="552087" cy="361847"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent2"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>29765</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>386953</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>41672</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="8" name="直線矢印コネクタ 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3D82751-BC89-4576-97F4-833AF5446B96}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1750219" y="4863703"/>
+          <a:ext cx="5953" cy="1047750"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>5953</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>148829</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>23271</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>100355</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D19AD40-2190-429E-B4AB-026DFE8E836A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="690562" y="13787438"/>
+          <a:ext cx="4124975" cy="2713776"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>17859</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>11907</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>658631</xdr:colOff>
+      <xdr:row>115</xdr:row>
+      <xdr:rowOff>111558</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="図 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35A303EE-84F0-4C35-AC73-1F948475C2A8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="702468" y="16758048"/>
+          <a:ext cx="2009991" cy="3207182"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>23812</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>136921</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>422672</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>71438</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="正方形/長方形 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6597446F-376C-4BDD-8387-61CEC1240D97}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1393031" y="16192499"/>
+          <a:ext cx="398860" cy="279798"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent2"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>279796</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>47624</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>291703</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>89296</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="17" name="直線矢印コネクタ 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D45262FF-F877-432F-ABEE-3291D2AAE294}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1649015" y="16621124"/>
+          <a:ext cx="11907" cy="1077516"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>398859</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>53578</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>595312</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>59531</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="19" name="直線コネクタ 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41593EA1-FCA8-459B-8094-68B4684501CB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1768078" y="6613922"/>
+          <a:ext cx="1565672" cy="5953"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>627277</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>154781</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="図 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91E36622-7338-44C7-A25C-D4F693470D86}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="684610" y="7250906"/>
+          <a:ext cx="3365714" cy="2226469"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>684609</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>297656</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>153646</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="図 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE492E23-4AF9-4AEF-9E45-B697C7DACC0E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="684609" y="9667876"/>
+          <a:ext cx="3036094" cy="3606458"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>541735</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>29767</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>212758</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>89298</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="正方形/長方形 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E72CB108-EE80-4645-8E27-ADD86FF5BE8E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1226344" y="9179720"/>
+          <a:ext cx="355633" cy="232172"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent2"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>11906</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>154781</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>17859</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>166687</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="25" name="直線矢印コネクタ 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{502E9C4B-3D60-4F4B-9455-DE631D78D51F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1381125" y="9477375"/>
+          <a:ext cx="5953" cy="1047750"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>577453</xdr:colOff>
+      <xdr:row>136</xdr:row>
+      <xdr:rowOff>170762</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="35" name="図 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2B2220C-2D48-4674-A3E0-E37798778E74}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="684610" y="20544235"/>
+          <a:ext cx="2631281" cy="3105652"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>138</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>631032</xdr:colOff>
+      <xdr:row>149</xdr:row>
+      <xdr:rowOff>166676</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="37" name="図 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65C1B55D-8131-4CCC-BF50-88CAE6556870}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="684610" y="23824406"/>
+          <a:ext cx="4054078" cy="2065723"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>547688</xdr:colOff>
+      <xdr:row>134</xdr:row>
+      <xdr:rowOff>154781</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>363140</xdr:colOff>
+      <xdr:row>136</xdr:row>
+      <xdr:rowOff>113109</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="38" name="正方形/長方形 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6261BA6B-73E8-45EB-A5DD-8E4A14D5A915}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1232297" y="23288625"/>
+          <a:ext cx="500062" cy="303609"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent2"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>137</xdr:row>
+      <xdr:rowOff>53578</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>144</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="40" name="直線矢印コネクタ 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B57C1D4-86AA-45AF-BD62-A8F808422D98}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1416844" y="23705344"/>
+          <a:ext cx="0" cy="1202531"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>547687</xdr:colOff>
+      <xdr:row>149</xdr:row>
+      <xdr:rowOff>148828</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>535781</xdr:colOff>
+      <xdr:row>149</xdr:row>
+      <xdr:rowOff>154781</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="42" name="直線コネクタ 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B93B92B2-844D-455F-A80C-8BE09B9BFFBA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1916906" y="25872281"/>
+          <a:ext cx="2726531" cy="5953"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>556460</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>7481</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{548A6A45-CAAF-4F99-AA11-9BA8207A05B5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="686803" y="852237"/>
+          <a:ext cx="1930065" cy="2393744"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>631658</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>45119</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>300790</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>125329</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="正方形/長方形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A961BEE-766D-466A-A7E7-D45113440BBF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1318461" y="2942724"/>
+          <a:ext cx="355934" cy="250658"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent2"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>684609</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>23813</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>434578</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>162479</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="図 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{777B70A6-D838-495A-BA2F-E8E1BD84DA3F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="684609" y="3649266"/>
+          <a:ext cx="2488407" cy="1865072"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>65171</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>65171</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>75199</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>5013</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="8" name="直線矢印コネクタ 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E72E4CEC-91CE-4716-9EE9-AE84689694D3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="1438776" y="3303671"/>
+          <a:ext cx="10028" cy="1814763"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>453378</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>161048</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>398233</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>166061</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="17" name="直線コネクタ 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0892C4AC-9A31-4541-B997-AD09FA856FD2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1822597" y="5512907"/>
+          <a:ext cx="1314074" cy="5013"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>684608</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>678655</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>70812</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="図 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D865F412-A799-4525-881E-F2B6A3BC1BF8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="684608" y="6042422"/>
+          <a:ext cx="4786313" cy="4214187"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1399,15 +5040,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>9095</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>39565</xdr:rowOff>
+      <xdr:rowOff>7328</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>78828</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1422,7 +5063,7 @@
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill>
+      <xdr:blipFill rotWithShape="1">
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
@@ -1430,14 +5071,13 @@
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
+        <a:srcRect r="61726"/>
+        <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="857250"/>
-          <a:ext cx="10058400" cy="3982915"/>
+          <a:off x="692267" y="861294"/>
+          <a:ext cx="2802423" cy="2896155"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1449,22 +5089,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>6569</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>162944</xdr:rowOff>
+      <xdr:colOff>463769</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>73373</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3924395D-4314-4D81-A68C-B2EE077D70DE}"/>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4FC1563-96C0-4E88-8E72-F03096CA45A2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1486,8 +5126,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="5143500"/>
-          <a:ext cx="10058400" cy="4963544"/>
+          <a:off x="689741" y="8939705"/>
+          <a:ext cx="10021614" cy="566703"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1496,118 +5136,18 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>666750</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>438150</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>33463</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="図 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76507172-78A0-4DBE-A27F-70B8C2CFF7F3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="666750" y="11772900"/>
-          <a:ext cx="10058400" cy="300163"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>73373</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="図 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4FC1563-96C0-4E88-8E72-F03096CA45A2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="685800" y="10858500"/>
-          <a:ext cx="10058400" cy="568673"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
+      <xdr:colOff>674076</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>7325</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:colOff>454268</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>109903</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1622,8 +5162,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1543050" y="4305300"/>
-          <a:ext cx="638175" cy="476250"/>
+          <a:off x="1362807" y="3377710"/>
+          <a:ext cx="468923" cy="271097"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -1667,33 +5207,31 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>490538</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:colOff>177362</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>36635</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>39414</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="14" name="直線矢印コネクタ 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72C5A8C9-AEA2-404E-9CEC-09BD201672ED}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="12" idx="2"/>
-        </xdr:cNvCxnSpPr>
+        <xdr:cNvPr id="8" name="直線矢印コネクタ 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{588190D4-AC74-473C-B5BD-4FD78C7BCB3E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1862138" y="4781550"/>
-          <a:ext cx="4762" cy="942975"/>
+        <a:xfrm flipH="1">
+          <a:off x="1543707" y="3794083"/>
+          <a:ext cx="13138" cy="1369124"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1722,6 +5260,211 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>683172</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>190547</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>95944</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="図 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82A34E64-F4E4-485B-BC7C-B1F8F1125485}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="683172" y="9906000"/>
+          <a:ext cx="9754961" cy="266737"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>684609</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>303609</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>16074</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="図 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74771E99-EF13-45CE-BC21-557723F76BEF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="684609" y="3970735"/>
+          <a:ext cx="3042047" cy="2087761"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>242847</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>155192</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>592438</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>161760</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="19" name="直線コネクタ 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{732CC1B4-01CB-48F9-A011-0FF678C78730}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="927456" y="4816489"/>
+          <a:ext cx="1034201" cy="6568"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>314739</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>173402</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="図 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D28E90D2-31AE-4121-BA1E-EF0DACC92149}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4124739" y="4000501"/>
+          <a:ext cx="3064565" cy="4173901"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1729,16 +5472,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>684609</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>305800</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>95838</xdr:rowOff>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>20180</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>29766</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1767,8 +5510,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="895350"/>
-          <a:ext cx="7163800" cy="4210638"/>
+          <a:off x="684609" y="863204"/>
+          <a:ext cx="4127837" cy="2446734"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1780,15 +5523,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>315326</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>124536</xdr:rowOff>
+      <xdr:colOff>11906</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>17858</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>672703</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>9017</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1817,8 +5560,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="5181600"/>
-          <a:ext cx="7173326" cy="5096586"/>
+          <a:off x="696515" y="3470671"/>
+          <a:ext cx="4083844" cy="2926049"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1930,14 +5673,14 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:colOff>117872</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>59530</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>470297</xdr:colOff>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1953,8 +5696,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="952500" y="4543425"/>
-          <a:ext cx="542925" cy="457200"/>
+          <a:off x="802481" y="2994421"/>
+          <a:ext cx="352425" cy="275035"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1995,18 +5738,68 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>29766</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>23813</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>109929</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="図 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF376C01-4212-48A5-B4BD-69430F0E6F28}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5476876" y="3482579"/>
+          <a:ext cx="4131468" cy="5604663"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>514350</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:colOff>317897</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>90488</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>523875</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:colOff>327422</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>119063</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2021,8 +5814,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1200150" y="5076825"/>
-          <a:ext cx="9525" cy="1057275"/>
+          <a:off x="1002506" y="3370660"/>
+          <a:ext cx="9525" cy="1064419"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2051,54 +5844,59 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>343809</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>20273</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="図 15">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF376C01-4212-48A5-B4BD-69430F0E6F28}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8229600" y="5181600"/>
-          <a:ext cx="6516009" cy="8764223"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>184547</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>41672</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>208359</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>41672</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="直線コネクタ 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C76733D-880D-4031-B357-9C3069494AA8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="869156" y="4702969"/>
+          <a:ext cx="708422" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -2108,23 +5906,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>684609</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>191580</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>124512</xdr:rowOff>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>482203</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>125110</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BF903D9-2454-455A-BA5E-5C8AC82F646B}"/>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C303A514-C0E4-4BE5-A22C-1E623BB385F5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2146,8 +5944,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="857250"/>
-          <a:ext cx="7735380" cy="4925112"/>
+          <a:off x="684609" y="863204"/>
+          <a:ext cx="2536032" cy="3060000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2159,22 +5957,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>220446</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>163001</xdr:rowOff>
+      <xdr:colOff>3411</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>12394</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>296432</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>457</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92D08D4C-C321-43D0-B28C-7D80F795A0F3}"/>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BF903D9-2454-455A-BA5E-5C8AC82F646B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2196,8 +5994,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="6381750"/>
-          <a:ext cx="9821646" cy="7706801"/>
+          <a:off x="688020" y="4155769"/>
+          <a:ext cx="5085287" cy="3268235"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2206,18 +6004,68 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>17860</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>157933</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>41672</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>648</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92D08D4C-C321-43D0-B28C-7D80F795A0F3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="702469" y="7926761"/>
+          <a:ext cx="4816078" cy="3813450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:colOff>59531</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>107156</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>541217</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>81377</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2232,8 +6080,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1562100" y="5276850"/>
-          <a:ext cx="638175" cy="409575"/>
+          <a:off x="1428750" y="3559969"/>
+          <a:ext cx="481686" cy="319502"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2276,16 +6124,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>598793</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>53577</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:colOff>482203</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>53852</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2299,9 +6147,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2762250" y="3152775"/>
-          <a:ext cx="1695450" cy="0"/>
+        <a:xfrm flipV="1">
+          <a:off x="1968012" y="5750718"/>
+          <a:ext cx="1252629" cy="275"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2331,16 +6179,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>566739</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>154781</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:colOff>446484</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>158354</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2354,9 +6202,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2762250" y="3924300"/>
-          <a:ext cx="1695450" cy="0"/>
+        <a:xfrm flipV="1">
+          <a:off x="1935958" y="6715125"/>
+          <a:ext cx="1248964" cy="3573"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2386,16 +6234,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>619124</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>29765</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>323850</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:colOff>464342</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>32146</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2409,9 +6257,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2743200" y="4667250"/>
-          <a:ext cx="1695450" cy="0"/>
+        <a:xfrm flipV="1">
+          <a:off x="1988343" y="6244828"/>
+          <a:ext cx="1214437" cy="2381"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2420,6 +6268,62 @@
           <a:solidFill>
             <a:srgbClr val="FF0000"/>
           </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>333376</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>172640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>339328</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>17859</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="18" name="直線矢印コネクタ 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{547D389F-E88C-482E-AF36-EA75E18E2965}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1702595" y="3970734"/>
+          <a:ext cx="5952" cy="1571625"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -3540,15 +7444,164 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>4252</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:colOff>10820</xdr:colOff>
+      <xdr:row>200</xdr:row>
+      <xdr:rowOff>156884</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>416719</xdr:colOff>
+      <xdr:row>207</xdr:row>
+      <xdr:rowOff>92633</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="55" name="図 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBDDEE7D-30B2-4B24-99F6-8BDFEF364904}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect b="59495"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="695429" y="34685009"/>
+          <a:ext cx="4513556" cy="1144233"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>5954</xdr:colOff>
+      <xdr:row>142</xdr:row>
+      <xdr:rowOff>166687</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>476251</xdr:colOff>
+      <xdr:row>159</xdr:row>
+      <xdr:rowOff>104348</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="47" name="図 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36103C72-5324-4D3E-AF96-C7093BD4C902}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="690563" y="24681656"/>
+          <a:ext cx="3893344" cy="2872551"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>684609</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>11907</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>520165</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>108858</xdr:rowOff>
+      <xdr:colOff>181862</xdr:colOff>
+      <xdr:row>134</xdr:row>
+      <xdr:rowOff>31606</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E680A21C-6A7B-48BB-809A-F9999AAA0EA8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="684609" y="18484454"/>
+          <a:ext cx="6343347" cy="4680996"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>15139</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>5444</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>500743</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>47696</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3556,6 +7609,506 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B2875B9-3E5B-4036-B3DE-E87151C2986E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="700939" y="1921330"/>
+          <a:ext cx="3914604" cy="2306480"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9016</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>165680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>681221</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>27214</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62A9540C-E8E4-4162-B9FF-E6E1E51D586C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="694816" y="4519966"/>
+          <a:ext cx="4101205" cy="2648277"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>44106</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>164224</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>522514</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>5353</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6B77559-B4D3-4944-B491-39569172638A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="729906" y="7827767"/>
+          <a:ext cx="4593208" cy="711986"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>18018</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>1126</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>16565</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>86390</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF21DB78-634B-4560-8A2B-887B3B9B3C66}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="705475" y="9045735"/>
+          <a:ext cx="3435829" cy="2346416"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>681795</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>2057</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>29308</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>9184</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4889C18-85F5-4E63-B51F-090671400A56}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="681795" y="11124326"/>
+          <a:ext cx="3479898" cy="2534916"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>675082</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>20240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>404811</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>104364</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="図 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E973615-A504-4EDB-9E20-9390BD5EE023}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="675082" y="14694693"/>
+          <a:ext cx="8629651" cy="256765"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>4580</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>159819</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>21981</xdr:colOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>80537</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D90EBD02-69B9-4518-AF44-81A4A37565A2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="693311" y="15158031"/>
+          <a:ext cx="4149785" cy="2617025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>5952</xdr:colOff>
+      <xdr:row>138</xdr:row>
+      <xdr:rowOff>11905</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>142874</xdr:colOff>
+      <xdr:row>139</xdr:row>
+      <xdr:rowOff>152745</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C425462F-E4C0-4589-A04E-ED7D9EFBF7A4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="690561" y="23836311"/>
+          <a:ext cx="10406063" cy="313481"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>13125</xdr:colOff>
+      <xdr:row>161</xdr:row>
+      <xdr:rowOff>27213</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>364671</xdr:colOff>
+      <xdr:row>170</xdr:row>
+      <xdr:rowOff>121072</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{252B817D-1247-4F5A-9AB5-83CB6DB2D361}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="698925" y="28068813"/>
+          <a:ext cx="3780546" cy="1661402"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>10886</xdr:colOff>
+      <xdr:row>174</xdr:row>
+      <xdr:rowOff>28644</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>157843</xdr:colOff>
+      <xdr:row>185</xdr:row>
+      <xdr:rowOff>30235</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="図 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DAB773E-FAC7-4F8B-91CB-CBE466BC9EF1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="696686" y="30334473"/>
+          <a:ext cx="2890157" cy="1917476"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2840</xdr:colOff>
+      <xdr:row>186</xdr:row>
+      <xdr:rowOff>162103</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>272144</xdr:colOff>
+      <xdr:row>197</xdr:row>
+      <xdr:rowOff>144082</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="図 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE562746-06A8-4C7B-B9B3-3CE868B9CEA2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3577,8 +8130,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="684609" y="2299608"/>
-          <a:ext cx="6639127" cy="4000500"/>
+          <a:off x="688640" y="32557989"/>
+          <a:ext cx="3012504" cy="1897864"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3590,22 +8143,1314 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>676275</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>159728</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>298434</xdr:colOff>
+      <xdr:colOff>683655</xdr:colOff>
+      <xdr:row>208</xdr:row>
+      <xdr:rowOff>163997</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>303609</xdr:colOff>
+      <xdr:row>219</xdr:row>
+      <xdr:rowOff>93346</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="図 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1ABF22F4-4B3D-41BB-85BC-647FCA213946}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="683655" y="36073247"/>
+          <a:ext cx="4412220" cy="1828396"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>683173</xdr:colOff>
+      <xdr:row>222</xdr:row>
+      <xdr:rowOff>140352</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>291354</xdr:colOff>
+      <xdr:row>238</xdr:row>
+      <xdr:rowOff>107995</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="図 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4144EA69-3B4E-4A52-9E08-AF29FF513F73}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="683173" y="37455940"/>
+          <a:ext cx="3709534" cy="2657055"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>7425</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>7139</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>220624</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>157843</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="図 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7492C659-B607-471E-A51D-90192FE9B58F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="693225" y="1052168"/>
+          <a:ext cx="5699599" cy="324875"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>47110</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>568684</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>136071</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="正方形/長方形 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14A3A873-71EB-4A28-A6C4-6E0B4388CE80}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="876300" y="3878881"/>
+          <a:ext cx="378184" cy="263133"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent2"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>337457</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>45795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>348718</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>97971</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="27" name="直線矢印コネクタ 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3ADE866A-EEB1-456A-B785-70EF3873B919}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="1023257" y="4225909"/>
+          <a:ext cx="11261" cy="1097205"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>239486</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>130629</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>108857</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>130629</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="30" name="直線コネクタ 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09EECC49-FC7D-42D8-BF42-8B3C803FEEDB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="925286" y="5529943"/>
+          <a:ext cx="555171" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>375556</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>70757</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>70381</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>163286</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="正方形/長方形 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB14B386-CCFF-4D4F-AEE9-F89CA36FC6AC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1061356" y="11043557"/>
+          <a:ext cx="380625" cy="266700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent2"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>532649</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>91778</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>541735</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>101203</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="33" name="直線矢印コネクタ 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D09A7A6-2AEC-44CA-9D3C-AE98FC5628B0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1217258" y="11313419"/>
+          <a:ext cx="9086" cy="872628"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>417700</xdr:colOff>
       <xdr:row>71</xdr:row>
-      <xdr:rowOff>163287</xdr:rowOff>
+      <xdr:rowOff>154782</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>321468</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>157481</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="37" name="直線コネクタ 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{461C6EB9-827F-4198-A1AA-FE6EBCB89C5D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="1102309" y="12412266"/>
+          <a:ext cx="588378" cy="2699"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>672703</xdr:colOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>17859</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>420004</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>141847</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="38" name="正方形/長方形 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{977103E5-9324-40CD-B7CD-DF6BAD04AD60}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1357312" y="17799843"/>
+          <a:ext cx="431911" cy="296629"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent2"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>208358</xdr:colOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>71437</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>214311</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="40" name="直線矢印コネクタ 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3AE5B9B9-90EA-48E5-9B9F-F10716C5117B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1577577" y="18198703"/>
+          <a:ext cx="5953" cy="1577578"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>523874</xdr:colOff>
+      <xdr:row>127</xdr:row>
+      <xdr:rowOff>95252</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>244078</xdr:colOff>
+      <xdr:row>127</xdr:row>
+      <xdr:rowOff>95252</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="42" name="直線コネクタ 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F38C65BA-9D4E-4066-81B0-6CC6B7BE6B7B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2577702" y="22020611"/>
+          <a:ext cx="1774032" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>535780</xdr:colOff>
+      <xdr:row>123</xdr:row>
+      <xdr:rowOff>53578</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>255984</xdr:colOff>
+      <xdr:row>123</xdr:row>
+      <xdr:rowOff>53578</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="43" name="直線コネクタ 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7DC5B5E-E7D0-436C-B073-11E0AE5CA586}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2589608" y="21288375"/>
+          <a:ext cx="1774032" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>541735</xdr:colOff>
+      <xdr:row>118</xdr:row>
+      <xdr:rowOff>148827</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>261939</xdr:colOff>
+      <xdr:row>118</xdr:row>
+      <xdr:rowOff>148827</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="44" name="直線コネクタ 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AA4FEA0-0FAF-4590-988E-6C86A8611A8E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2595563" y="20520421"/>
+          <a:ext cx="1774032" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>602909</xdr:colOff>
+      <xdr:row>157</xdr:row>
+      <xdr:rowOff>158207</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>348156</xdr:colOff>
+      <xdr:row>159</xdr:row>
+      <xdr:rowOff>39414</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="45" name="正方形/長方形 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03A346EF-FDF0-4880-8BE9-5FAEBABBAF4B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1286081" y="26972724"/>
+          <a:ext cx="428420" cy="222793"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent2"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>141514</xdr:colOff>
+      <xdr:row>160</xdr:row>
+      <xdr:rowOff>40771</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>150630</xdr:colOff>
+      <xdr:row>166</xdr:row>
+      <xdr:rowOff>125186</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="46" name="直線矢印コネクタ 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C0924AC-F102-43C9-BA62-7F3CDC65867B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="1513114" y="27908200"/>
+          <a:ext cx="9116" cy="1129443"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>293914</xdr:colOff>
+      <xdr:row>183</xdr:row>
+      <xdr:rowOff>73125</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>639675</xdr:colOff>
+      <xdr:row>184</xdr:row>
+      <xdr:rowOff>103415</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="48" name="正方形/長方形 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BBCC966-FEBA-431B-98F9-F6DCD946E6F2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="979714" y="31946496"/>
+          <a:ext cx="345761" cy="204462"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent2"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>580191</xdr:colOff>
+      <xdr:row>184</xdr:row>
+      <xdr:rowOff>154597</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>583660</xdr:colOff>
+      <xdr:row>187</xdr:row>
+      <xdr:rowOff>48638</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="49" name="直線矢印コネクタ 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC490D65-1024-47F0-B1D0-91BAF7283881}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1265180" y="31477661"/>
+          <a:ext cx="3469" cy="404743"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>571499</xdr:colOff>
+      <xdr:row>205</xdr:row>
+      <xdr:rowOff>47624</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>514878</xdr:colOff>
+      <xdr:row>206</xdr:row>
+      <xdr:rowOff>164224</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="51" name="正方形/長方形 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79EB807F-1DEF-45F9-8914-8D75BCDE7B3E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3309937" y="35438952"/>
+          <a:ext cx="627988" cy="289241"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent2"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>244634</xdr:colOff>
+      <xdr:row>207</xdr:row>
+      <xdr:rowOff>103944</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>247773</xdr:colOff>
+      <xdr:row>215</xdr:row>
+      <xdr:rowOff>82523</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="52" name="直線矢印コネクタ 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{126B2741-5D51-4B02-BA16-074CE8593DB3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3667681" y="35840553"/>
+          <a:ext cx="3139" cy="1359704"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>549729</xdr:colOff>
+      <xdr:row>187</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>566057</xdr:colOff>
+      <xdr:row>191</xdr:row>
+      <xdr:rowOff>103414</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="56" name="正方形/長方形 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{182203F5-B829-4AD2-83F5-BE4E36A5D500}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1235529" y="32684357"/>
+          <a:ext cx="2073728" cy="685800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent2"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>683172</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>675409</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>52433</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BA5CF7E-0AE5-4CFD-9EB1-B4872DB1E2C3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="683172" y="865909"/>
+          <a:ext cx="4148601" cy="2303797"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>17318</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>60097</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="5" name="図 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62A9540C-E8E4-4162-B9FF-E6E1E51D586C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD56E484-7D4F-40E4-93A6-5E0BAAD54F1B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3627,8 +9472,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="676275" y="8473692"/>
-          <a:ext cx="6425730" cy="4248988"/>
+          <a:off x="688731" y="3201866"/>
+          <a:ext cx="4149702" cy="2587885"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3637,25 +9482,314 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>505556</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>84992</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>167052</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>139211</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="正方形/長方形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8544A1FB-93FF-4A1C-A209-493C4546999F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1194287" y="2781300"/>
+          <a:ext cx="350227" cy="222738"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent2"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>675543</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>67408</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>685068</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>38833</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="8" name="直線矢印コネクタ 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB73FC18-52A5-4082-9E68-AE484F2CCC15}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="1364274" y="3100754"/>
+          <a:ext cx="9525" cy="1151060"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>466724</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>65942</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>36635</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>70338</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="10" name="直線コネクタ 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5CD6DE8-9D12-41EB-8B8B-579FB0B89B2E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="1844186" y="4447442"/>
+          <a:ext cx="947372" cy="4396"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>418367</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>124558</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>43962</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>126756</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="11" name="直線コネクタ 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2783BA9-61E0-4A8A-812E-CF2EA7C1FFBE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="1795829" y="4843096"/>
+          <a:ext cx="1003056" cy="2198"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>386861</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>21981</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>65942</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>25644</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="12" name="直線コネクタ 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EAA6FD4-67F3-49A9-B36A-28E1C314546A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="1764323" y="5246077"/>
+          <a:ext cx="1056542" cy="3663"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>581872</xdr:colOff>
-      <xdr:row>93</xdr:row>
-      <xdr:rowOff>66804</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>681405</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>139213</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>674077</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>117419</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="図 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6B77559-B4D3-4944-B491-39569172638A}"/>
+        <xdr:cNvPr id="17" name="図 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{705FA64D-41E5-44C6-9216-361C019C7A15}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3664,7 +9798,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -3677,8 +9811,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="15087600"/>
-          <a:ext cx="6068272" cy="924054"/>
+          <a:off x="681405" y="6374425"/>
+          <a:ext cx="2747595" cy="2000436"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3687,25 +9821,30 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>238553</xdr:colOff>
-      <xdr:row>123</xdr:row>
-      <xdr:rowOff>163286</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>684609</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>23813</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>165827</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="図 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF21DB78-634B-4560-8A2B-887B3B9B3C66}"/>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BCAB611E-0016-43CB-8F77-4590B63EED58}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3714,7 +9853,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -3727,8 +9866,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="680358" y="16981714"/>
-          <a:ext cx="7042124" cy="4939393"/>
+          <a:off x="684609" y="2268141"/>
+          <a:ext cx="3423047" cy="1350499"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3739,23 +9878,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>136</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>610598</xdr:colOff>
-      <xdr:row>165</xdr:row>
-      <xdr:rowOff>81643</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>684609</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>166687</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>23813</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>25772</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="図 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4889C18-85F5-4E63-B51F-090671400A56}"/>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{926A90B6-CFD1-4F51-A087-5FB9AAB17C4C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3764,7 +9903,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -3777,8 +9916,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="680357" y="24057429"/>
-          <a:ext cx="6733812" cy="5211535"/>
+          <a:off x="684609" y="857250"/>
+          <a:ext cx="3446860" cy="1067569"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3787,204 +9926,190 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>181</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>416169</xdr:colOff>
-      <xdr:row>182</xdr:row>
-      <xdr:rowOff>125096</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="図 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E973615-A504-4EDB-9E20-9390BD5EE023}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="688731" y="30501981"/>
-          <a:ext cx="10058400" cy="293615"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>669471</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>55789</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>570986</xdr:colOff>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>122109</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>127919</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>464633</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>9293</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="吹き出し: 角を丸めた四角形 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA95B35D-B2BB-4A11-9767-73FA63AAE242}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4248060" y="815578"/>
+          <a:ext cx="2405500" cy="569032"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -39692"/>
+            <a:gd name="adj2" fmla="val 101906"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="+mn-ea"/>
+              <a:ea typeface="+mn-ea"/>
+            </a:rPr>
+            <a:t>ステップ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="+mn-ea"/>
+              <a:ea typeface="+mn-ea"/>
+            </a:rPr>
+            <a:t>1.128</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="+mn-ea"/>
+              <a:ea typeface="+mn-ea"/>
+            </a:rPr>
+            <a:t>文字以上入力を試みてそれをコピーする</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>29766</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>122594</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="図 14">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C8D1056-0DBD-4B2A-AA57-9464A2F2704B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7473042" y="2355396"/>
-          <a:ext cx="6024730" cy="951269"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>185</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>38967</xdr:colOff>
-      <xdr:row>208</xdr:row>
-      <xdr:rowOff>57708</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D90EBD02-69B9-4518-AF44-81A4A37565A2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="685800" y="31718250"/>
-          <a:ext cx="6211167" cy="4001058"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>209</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>181862</xdr:colOff>
-      <xdr:row>236</xdr:row>
-      <xdr:rowOff>19699</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="図 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E680A21C-6A7B-48BB-809A-F9999AAA0EA8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="685800" y="35833050"/>
-          <a:ext cx="6354062" cy="4648849"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
+      <xdr:rowOff>85484</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>412204</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>50525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="吹き出し: 角を丸めた四角形 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9C50134-0DBE-40EE-BC22-641A4E664B88}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2083594" y="3193015"/>
+          <a:ext cx="2436266" cy="482963"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -66641"/>
+            <a:gd name="adj2" fmla="val 20075"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="+mn-ea"/>
+              <a:ea typeface="+mn-ea"/>
+            </a:rPr>
+            <a:t>ステップ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="+mn-ea"/>
+              <a:ea typeface="+mn-ea"/>
+            </a:rPr>
+            <a:t>2.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="+mn-ea"/>
+              <a:ea typeface="+mn-ea"/>
+            </a:rPr>
+            <a:t>メモ帳に張り付けて</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
+              <a:latin typeface="+mn-ea"/>
+              <a:ea typeface="+mn-ea"/>
+            </a:rPr>
+            <a:t>127</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:latin typeface="+mn-ea"/>
+              <a:ea typeface="+mn-ea"/>
+            </a:rPr>
+            <a:t>文字までしか入力できないことを確認</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -4325,8 +10450,235 @@
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{040A64B8-4E1E-48F4-A1FE-C8C4C08F9C5C}">
+  <dimension ref="B2:B5"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B4" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B5" s="5"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0771CA-5847-4081-9CE1-80252A4D320F}">
+  <dimension ref="B2:B146"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B37" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B66" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B102" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="146" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94DFA663-1173-4383-A0C0-A67BCDAA6E9A}">
+  <dimension ref="B2:B50"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B2" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B4" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B50" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6BBB370-8A42-42EE-B5FC-E817BC42ECE4}">
+  <dimension ref="B2:B4"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B2" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B4" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F02CE59B-B5EE-4F32-B024-56DB44B88B48}">
+  <dimension ref="B2:B4"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B4" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91FB7FDE-4389-4DA6-BE1E-C09A313712E8}">
+  <dimension ref="B2:B30"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B2" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B30" t="s">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B6AD7C9-CDE8-4F75-9F83-73C913947542}">
+  <dimension ref="B2:B118"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B2" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B41" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B79" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B118" t="s">
+        <v>79</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{925E0D86-D402-473B-B2F7-E46027B2B604}">
+  <dimension ref="B2:B34"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B34" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -4347,12 +10699,12 @@
   <sheetData>
     <row r="1" spans="2:40" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="2" spans="2:40" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="2:40" ht="15" x14ac:dyDescent="0.25">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4418,7 +10770,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDB1C250-7ABD-4E81-92B5-3B68C1BA5E17}">
-  <dimension ref="B2:Q68"/>
+  <dimension ref="B2:G57"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.15">
@@ -4428,27 +10780,27 @@
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="7:7" x14ac:dyDescent="0.15">
+      <c r="G23" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B49" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="17:17" x14ac:dyDescent="0.15">
-      <c r="Q30" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="61" spans="2:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="B61" s="1" t="s">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B51" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B63" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B68" t="s">
-        <v>20</v>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B57" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -4461,32 +10813,32 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C27E20C7-D0B2-4151-B82E-BD4F8F2CA820}">
-  <dimension ref="B2:M88"/>
+  <dimension ref="B2:I88"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="2" spans="2:2" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B2" s="1" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
-    <row r="30" spans="13:13" x14ac:dyDescent="0.15">
-      <c r="M30" t="s">
-        <v>28</v>
+    <row r="20" spans="9:9" x14ac:dyDescent="0.15">
+      <c r="I20" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="83" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B83" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="88" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B88" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -4498,22 +10850,22 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02A7BC2A-B47B-44D9-96C7-5B74F75C82B3}">
-  <dimension ref="B2:B36"/>
+  <dimension ref="B2:B45"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
-    <row r="36" spans="2:2" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="B36" s="1" t="s">
-        <v>26</v>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B45" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -4529,74 +10881,74 @@
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B3" s="2"/>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B4" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B5" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B6" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B7" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B3" s="3"/>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B4" s="3" t="s">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B8" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B5" s="3" t="s">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B9" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B6" s="3" t="s">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B10" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B7" s="3" t="s">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B11" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B8" s="3" t="s">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B12" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B9" s="3" t="s">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B13" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B10" s="3" t="s">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B14" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B11" s="3" t="s">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B15" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B12" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B13" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B14" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B15" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="M15" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -4608,68 +10960,124 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{260A926D-6497-4D4A-B3E1-0AB8B83F8D79}">
-  <dimension ref="B2:B185"/>
+  <dimension ref="B2:B222"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B9" t="s">
-        <v>48</v>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B5" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B44" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B51" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B84" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="89" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B89" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="137" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B137" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="142" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B142" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B173" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B11" t="s">
+    <row r="200" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B200" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="222" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B222" t="s">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64D94B4F-9DF3-4C0B-912D-B2F2F1D2BC39}">
+  <dimension ref="B2:B37"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B2" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B12" t="s">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B13" t="s">
+    <row r="37" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B37" s="4" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B87" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="96" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B96" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="181" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B181" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="185" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B185" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABFE6C07-D0C2-4BB2-BF49-684C13174E9F}">
+  <dimension ref="B2:B4"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B4" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -4849,15 +11257,15 @@
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8048152-0CA9-47E5-A6CC-6D3980A2E781}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="dab87824-9c6b-4a08-9c96-9c9ea904f12c"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="dab87824-9c6b-4a08-9c96-9c9ea904f12c"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/extra/report/No.課題4_テスト結果.xlsx
+++ b/extra/report/No.課題4_テスト結果.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED26FD92-8F59-4E49-8514-929C55534DC7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{544B04FB-DBC0-42E6-BAA6-C0B174C772BA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="10" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="4" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="前提" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="83">
   <si>
     <t>【前提】</t>
     <rPh sb="1" eb="3">
@@ -48,9 +48,6 @@
       <t>ズ</t>
     </rPh>
     <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>データーベースに登録済みのユーザー情報が表示される</t>
   </si>
   <si>
     <t>料金新規追加画面を確認する</t>
@@ -113,25 +110,15 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>12.「料金名」に”月額料金”「月額料金」に”1000”「加入日」に”2025年8月19日”「解約日に」”2025年9月19日”を記載して保存ボタンを押下した時に、料金編集画面に遷移する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>13.項目12を実行した後にデーターベースに「料金名」に”月額料金”「月額料金」に”1000”「加入日」に”2025年8月19日”「解約日」に”2025年9月19”日と記載された料金情報が存在することを確認</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>■料金テーブルのカラムがわかるように張っておきました</t>
-    <rPh sb="1" eb="3">
-      <t>リョウキン</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>ハ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>14.「料金名」に”月額料金”「月額料金」に”1000”「加入日」に”2025年8月20日”を記載して保存ボタンを押下した時に、料金編集画面に遷移する</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>15.項目13を実行した後にデーターベースに「料金名」に”月額料金”「月額料金」に”1000”「加入日」に”2025年8月20日”と記載された料金情報が存在することを確認する</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -209,56 +196,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>30.料金番号”1”の料金情報の「料金名」に”通常”「月額料金」に”2000”「加入日」に”2025年9月1日”「解約日」に”2025年10月01日”に変更して保存ボタンを押下した時に、料金編集テキストの下に”保存しました。”と表示される</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>31.データーベースにある料金番号”1”のレコードが「料金名」が”通常”「月額料金」が”2000”「加入日」が”2025年9月1日”「解約日」が”2025年10月01日”となっていることを確認する</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>32.料金番号”2”の料金情報の必須項目である「料金名」に”通常“「月額料金」に”1000”「加入日」に”2025年10月1日”を記載して保存ボタンを押下した時に、料金編集テキストの下に”保存しました。”と表示される</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>33.データーベースにある料金番号”2”のレコードが「料金名」が”通常”「月額料金」が”1000”「加入日」が”2025年10月1日”となっていることを確認する</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>35.データーベースにある料金番号”12”のレコードが「料金名」が”通常”「月額料金」が”5000”「加入日」が”2025年8月18日”「解約日」が”2025年8月18日”のまま変更されていないことを確認する</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>36.キャンセルボタンを押下した時に料金情報検索画面に遷移する。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>38.料金番号“15”の料金情報編集画面で削除ボタンを押下した時に、OKボタンを押下すると料金情報検索画面に遷移する</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>39.項目38を実行した後にデーターベースに料金番号”15”のレコードが存在しないことを確認する</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>■料金テーブルのカラムがわかるように張っておきます</t>
-    <rPh sb="1" eb="3">
-      <t>リョウキン</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>ハ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>34.料金番号”12”の料金情報に全て空欄で保存ボタンを押下したときに、「料金」「月額料金」「加入日」の欄の下に”この項目の入力は必須です。”と表示される</t>
-    <rPh sb="22" eb="24">
-      <t>ホゾン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>37.料金番号“15”の料金情報編集画面で削除ボタンを押下した時に、ブラウザ上部に”id:15を削除してもよろしいですか？”と表示される</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -290,9 +228,6 @@
       <t>”と表示される</t>
     </r>
     <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>項目40を実行した後にデーターベースに全カラムになにも情報がないレコードが存在しないことを確認する</t>
   </si>
   <si>
     <t>料金新規追加画面の料金名の入力チェック</t>
@@ -332,6 +267,31 @@
   </si>
   <si>
     <t>料金新規追加画面で不正な値を入力して保存ボタンを押下</t>
+  </si>
+  <si>
+    <r>
+      <t>「月額料金」で数字以外を入力して保存ボタンを押下した時に、月額料金の欄の下に”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>不正な値が入力されています。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>”と表示される</t>
+    </r>
   </si>
   <si>
     <r>
@@ -420,20 +380,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>12.「料金名」に”月額料金”「月額料金」に”2000”「加入日」に”2025年8月19日”「解約日に」”2025年9月19日”を記載して保存ボタンを押下した時に、料金編集画面に遷移する</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>項目13のテスト結果</t>
-    <rPh sb="0" eb="2">
-      <t>コウモク</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ケッカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>■詳細設計書</t>
     <rPh sb="1" eb="6">
       <t>ショウサイセッケイショ</t>
@@ -464,23 +410,104 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>料金編集画面で不正な値を入力する</t>
+    <t>59.項目58を実行した後にデーターベースの「月額料金」カラムに数字以外の値が入っているレコードが存在しないことを確認する</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>58.「月額料金」で数字以外を入力して保存ボタンを押下した時に、データーベースに情報が保存されないことを確認</t>
+    <t>データーベースに料金テーブル作成済み</t>
+    <rPh sb="8" eb="10">
+      <t>リョウキン</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>サクセイズ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>59.項目58を実行した後にデーターベースの「月額料金」カラムに数字以外の値が入っているレコードが存在しないことを確認する</t>
+    <t>15.項目14実行した後にデーターベースに”月額料金”「月額料金」に”1000”「加入日」に”2025年8月20日”と記載された料金情報が存在することを確認する</t>
+    <rPh sb="3" eb="5">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>アト</t>
+    </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30.料金番号”46”の料金情報の「料金名」に”通常”「月額料金」に”2000”「加入日」に”2025年9月1日”「解約日」に”2025年10月01日”に変更して保存ボタンを押下した時に、料金編集テキストの下に”保存しました。”と表示される</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>31.データーベースにある料金番号”46”のレコードが「料金名」が”通常”「月額料金」が”2000”「加入日」が”2025年9月1日”「解約日」が”2025年10月01日”となっていることを確認する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>32.料金番号”47”の料金情報の必須項目である「料金名」に”通常“「月額料金」に”1000”「加入日」に”2025年10月01日”を記載して保存ボタンを押下した時に、料金編集テキストの下に”保存しました。”と表示される</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>34.料金番号”47”の料金情報に全て空欄で保存ボタンを押下したときに、「料金」「月額料金」「加入日」の欄の下に”この項目の入力は必須です。”と表示される</t>
+    <rPh sb="22" eb="24">
+      <t>ホゾン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>35.データーベースにある料金番号”47”のレコードが「料金名」が”通常”「月額料金」が”1000”「加入日」が”2025年10月01日”「解約日」が”null”のまま変更されていないことを確認する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>33.データーベースにある料金番号”47”のレコードが「料金名」が”通常”「月額料金」が”1000”「加入日」が”2025年10月01日”「解約日」が"null"となっていることを確認する</t>
+    <rPh sb="70" eb="73">
+      <t>カイヤクビ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>37.料金番号“47”の料金情報編集画面で削除ボタンを押下した時に、ブラウザ上部に”id:47を削除してもよろしいですか？”と表示される</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>38.料金番号“47”の料金情報編集画面で削除ボタンを押下した時に、OKボタンを押下すると料金情報検索画面に遷移する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>39.項目38を実行した後にデーターベースに料金番号”47”のレコードが存在しないことを確認する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>41.項目40を実行した後にデーターベースに全カラムになにも情報がないレコードが存在しないことを確認する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デベロッパーツールで月額料金の値"1000000000"</t>
+    <rPh sb="10" eb="14">
+      <t>ゲツガクリョウキン</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>アタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>■入力方法</t>
+    <rPh sb="1" eb="5">
+      <t>ニュウリョクホウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>料金編集画面で不正な値を入力して保存ボタンを押下</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -494,6 +521,13 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
@@ -526,12 +560,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
@@ -571,14 +619,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -602,21 +651,21 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>43276</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>324565</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>57206</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF7209C9-F0D3-4C13-8165-17377D432703}"/>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9063C6C-C48F-43F8-AA13-CFC5BA5DCA42}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -638,8 +687,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="1066800"/>
-          <a:ext cx="10058400" cy="6558376"/>
+          <a:off x="685800" y="857250"/>
+          <a:ext cx="5125165" cy="400106"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -655,16 +704,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>685799</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>448120</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>60195</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>156458</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -693,8 +742,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="870857"/>
-          <a:ext cx="3191320" cy="2324424"/>
+          <a:off x="685799" y="857250"/>
+          <a:ext cx="3585459" cy="2571750"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -710,23 +759,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>672286</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>13139</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>123</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>105679</xdr:rowOff>
+      <xdr:colOff>143278</xdr:colOff>
+      <xdr:row>148</xdr:row>
+      <xdr:rowOff>29179</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{119866D4-301D-4A43-8EAC-56BE8B89A69E}"/>
+        <xdr:cNvPr id="64" name="図 63">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21391571-2448-477A-81D1-71CF81DA45CF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -748,8 +797,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="672286" y="4112173"/>
-          <a:ext cx="2743576" cy="1800472"/>
+          <a:off x="685800" y="21088350"/>
+          <a:ext cx="2886478" cy="4324954"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -760,23 +809,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>684608</xdr:colOff>
-      <xdr:row>119</xdr:row>
-      <xdr:rowOff>172639</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>416718</xdr:colOff>
-      <xdr:row>130</xdr:row>
-      <xdr:rowOff>124941</xdr:rowOff>
+      <xdr:colOff>86120</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>19651</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="47" name="図 46">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5580952D-1B52-48EE-8D1E-CB782D6723D7}"/>
+        <xdr:cNvPr id="59" name="図 58">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01F6AF19-9C17-45E1-87A4-AB0992FE8D1F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -798,8 +847,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="684608" y="20716873"/>
-          <a:ext cx="3155157" cy="1851349"/>
+          <a:off x="685800" y="12172950"/>
+          <a:ext cx="2829320" cy="4305901"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -811,22 +860,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>5434</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>149087</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>32203</xdr:rowOff>
+      <xdr:colOff>15061</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>22663</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>160417</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="36" name="図 35">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3C98C44-D2DB-4441-A40F-A1EC6DFC880F}"/>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{119866D4-301D-4A43-8EAC-56BE8B89A69E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -848,8 +897,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="692891" y="11628783"/>
-          <a:ext cx="2056935" cy="2840007"/>
+          <a:off x="700861" y="4823263"/>
+          <a:ext cx="4395014" cy="2880954"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -860,23 +909,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>683172</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>184733</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>91110</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>8333</xdr:colOff>
+      <xdr:row>174</xdr:row>
+      <xdr:rowOff>29764</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>103147</xdr:colOff>
+      <xdr:row>190</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="図 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{070722C5-13E8-4D93-B81E-07CA6EE0C4B1}"/>
+        <xdr:cNvPr id="47" name="図 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5580952D-1B52-48EE-8D1E-CB782D6723D7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -898,8 +947,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="683172" y="869675"/>
-          <a:ext cx="2251387" cy="3048000"/>
+          <a:off x="694133" y="29871589"/>
+          <a:ext cx="4895414" cy="2846786"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -908,18 +957,118 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>5433</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>15736</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>17116</xdr:colOff>
+      <xdr:row>121</xdr:row>
+      <xdr:rowOff>171449</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="36" name="図 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3C98C44-D2DB-4441-A40F-A1EC6DFC880F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="691233" y="17160736"/>
+          <a:ext cx="2754883" cy="3756163"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>6897</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>657225</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>149052</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{070722C5-13E8-4D93-B81E-07CA6EE0C4B1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="692697" y="809625"/>
+          <a:ext cx="2707728" cy="3625677"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>593271</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>119930</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>357539</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>81643</xdr:rowOff>
+      <xdr:colOff>21770</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>148505</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>571499</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -934,8 +1083,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1279071" y="3603359"/>
-          <a:ext cx="450068" cy="310055"/>
+          <a:off x="1393370" y="4091855"/>
+          <a:ext cx="549729" cy="327745"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -979,15 +1128,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>123967</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>155215</xdr:rowOff>
+      <xdr:colOff>295417</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>69490</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>124810</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>52552</xdr:rowOff>
+      <xdr:colOff>296260</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>138277</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1002,8 +1151,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1490312" y="3912663"/>
-          <a:ext cx="843" cy="1092889"/>
+          <a:off x="1667017" y="4527190"/>
+          <a:ext cx="843" cy="1097487"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1035,15 +1184,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>4317</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:colOff>13842</xdr:colOff>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>162160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>39247</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>5331</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1059,7 +1208,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1072,8 +1221,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="690117" y="6606503"/>
-          <a:ext cx="1406530" cy="1906126"/>
+          <a:off x="699642" y="8220310"/>
+          <a:ext cx="2734689" cy="3647840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1082,68 +1231,18 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>5444</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>174171</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>664030</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>11134</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="図 15">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD0CF1A9-7A31-42FE-BF26-78CCD288C985}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="691244" y="8708571"/>
-          <a:ext cx="1344386" cy="2275363"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>375556</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>143464</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>655451</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:colOff>23131</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>152989</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1158,8 +1257,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1061356" y="8329521"/>
-          <a:ext cx="279895" cy="204880"/>
+          <a:off x="1394731" y="11468689"/>
+          <a:ext cx="595994" cy="428036"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1202,16 +1301,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>503109</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>67442</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>511392</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>42595</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>339943</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>19817</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1225,9 +1324,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="1188909" y="8601842"/>
-          <a:ext cx="8283" cy="1368524"/>
+        <a:xfrm>
+          <a:off x="1711543" y="12021317"/>
+          <a:ext cx="2957" cy="1608958"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1258,16 +1357,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>571499</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>77390</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>303608</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>23812</xdr:rowOff>
+      <xdr:colOff>66674</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>96439</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>121</xdr:row>
+      <xdr:rowOff>161924</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1282,8 +1381,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1256108" y="14061281"/>
-          <a:ext cx="416719" cy="291703"/>
+          <a:off x="1438274" y="20498989"/>
+          <a:ext cx="609601" cy="408385"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1326,16 +1425,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>5953</xdr:colOff>
-      <xdr:row>102</xdr:row>
-      <xdr:rowOff>166687</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>684609</xdr:colOff>
-      <xdr:row>118</xdr:row>
-      <xdr:rowOff>105698</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>682228</xdr:colOff>
+      <xdr:row>151</xdr:row>
+      <xdr:rowOff>23812</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>9018</xdr:colOff>
+      <xdr:row>172</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1351,7 +1450,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1364,8 +1463,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="690562" y="17776031"/>
-          <a:ext cx="2047875" cy="2701261"/>
+          <a:off x="682228" y="25922287"/>
+          <a:ext cx="2755790" cy="3605213"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1377,15 +1476,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>410766</xdr:colOff>
-      <xdr:row>116</xdr:row>
-      <xdr:rowOff>152710</xdr:rowOff>
+      <xdr:colOff>534590</xdr:colOff>
+      <xdr:row>169</xdr:row>
+      <xdr:rowOff>133659</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>137440</xdr:colOff>
-      <xdr:row>118</xdr:row>
-      <xdr:rowOff>107156</xdr:rowOff>
+      <xdr:colOff>419099</xdr:colOff>
+      <xdr:row>172</xdr:row>
+      <xdr:rowOff>28574</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1400,8 +1499,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1095375" y="20179023"/>
-          <a:ext cx="411284" cy="299727"/>
+          <a:off x="1220390" y="29118234"/>
+          <a:ext cx="570309" cy="409265"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1444,16 +1543,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>119</xdr:row>
-      <xdr:rowOff>26142</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>588065</xdr:colOff>
-      <xdr:row>127</xdr:row>
-      <xdr:rowOff>158664</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>172</xdr:row>
+      <xdr:rowOff>149967</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>140390</xdr:colOff>
+      <xdr:row>181</xdr:row>
+      <xdr:rowOff>111039</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1468,8 +1567,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="1256109" y="20570376"/>
-          <a:ext cx="16565" cy="1513647"/>
+          <a:off x="1495425" y="29648892"/>
+          <a:ext cx="16565" cy="1504122"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1500,16 +1599,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>62377</xdr:colOff>
-      <xdr:row>130</xdr:row>
-      <xdr:rowOff>98096</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>410766</xdr:colOff>
-      <xdr:row>130</xdr:row>
-      <xdr:rowOff>101203</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>138577</xdr:colOff>
+      <xdr:row>190</xdr:row>
+      <xdr:rowOff>88571</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>190</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1524,8 +1623,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1431596" y="22541377"/>
-          <a:ext cx="2402217" cy="3107"/>
+          <a:off x="2195977" y="32673596"/>
+          <a:ext cx="3376148" cy="6679"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1553,68 +1652,18 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>6990</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>159181</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>11907</xdr:colOff>
-      <xdr:row>99</xdr:row>
-      <xdr:rowOff>124293</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="図 48">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78D55993-0D19-4F75-AD22-1D5F2E8F0A53}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="691599" y="14660994"/>
-          <a:ext cx="2058746" cy="2554721"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>65484</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>122</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>77390</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:colOff>334565</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1629,8 +1678,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="1434703" y="14424422"/>
-          <a:ext cx="11906" cy="1381125"/>
+          <a:off x="1695450" y="21002625"/>
+          <a:ext cx="10715" cy="1647825"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1661,16 +1710,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>341586</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>98534</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>670034</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>98534</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>151086</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>127109</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1685,8 +1734,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1707931" y="5905500"/>
-          <a:ext cx="1694793" cy="0"/>
+          <a:off x="2208486" y="7670909"/>
+          <a:ext cx="2811189" cy="6241"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2001,22 +2050,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>5437</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>51</xdr:row>
-      <xdr:rowOff>16565</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>53658</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>4955</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="図 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16DEEE84-DBB5-4D42-A8F6-2A66B11A5529}"/>
+        <xdr:cNvPr id="28" name="図 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88E220B6-1ABD-46FA-B1BD-291139612187}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2025,7 +2074,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2038,8 +2087,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="691237" y="8760515"/>
-          <a:ext cx="4109363" cy="3294643"/>
+          <a:off x="685800" y="8743950"/>
+          <a:ext cx="10058400" cy="1548005"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2061,10 +2110,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>672941</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>45983</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>102051</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2093,8 +2142,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="683172" y="853966"/>
-          <a:ext cx="5455148" cy="1583120"/>
+          <a:off x="683172" y="857250"/>
+          <a:ext cx="6851103" cy="1988001"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2105,16 +2154,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>22787</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>8210</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>101105</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>48427</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>680011</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>27260</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>165292</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2143,8 +2192,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="707396" y="2770460"/>
-          <a:ext cx="4870584" cy="1939264"/>
+          <a:off x="680011" y="3113360"/>
+          <a:ext cx="6863789" cy="2709782"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2155,16 +2204,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>11814</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>48153</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>388530</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>119062</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>497589</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>10053</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>188505</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>80962</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2179,13 +2228,13 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3434861" y="1256637"/>
-          <a:ext cx="2430544" cy="588831"/>
+          <a:off x="7355589" y="181503"/>
+          <a:ext cx="2434116" cy="585259"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRoundRectCallout">
           <a:avLst>
-            <a:gd name="adj1" fmla="val -23853"/>
-            <a:gd name="adj2" fmla="val 81492"/>
+            <a:gd name="adj1" fmla="val -35984"/>
+            <a:gd name="adj2" fmla="val 92884"/>
             <a:gd name="adj3" fmla="val 16667"/>
           </a:avLst>
         </a:prstGeom>
@@ -2241,16 +2290,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>437247</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>97918</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>135075</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>62959</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>418197</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>59818</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>116025</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2265,13 +2314,13 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2491075" y="4241293"/>
-          <a:ext cx="2436266" cy="482963"/>
+          <a:off x="3161397" y="5546218"/>
+          <a:ext cx="2441028" cy="559307"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRoundRectCallout">
           <a:avLst>
-            <a:gd name="adj1" fmla="val -66641"/>
-            <a:gd name="adj2" fmla="val 20075"/>
+            <a:gd name="adj1" fmla="val -70153"/>
+            <a:gd name="adj2" fmla="val -25624"/>
             <a:gd name="adj3" fmla="val 16667"/>
           </a:avLst>
         </a:prstGeom>
@@ -2401,23 +2450,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>683172</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>666750</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>161248</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114699</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>162498</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{512F4A59-2E8C-4882-8ACA-B25115D362E9}"/>
+        <xdr:cNvPr id="17" name="図 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F6D45A7-BA42-4457-B6B5-CC7AD5E38A4D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2426,7 +2475,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2439,8 +2488,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="683172" y="863204"/>
-          <a:ext cx="1352797" cy="2232935"/>
+          <a:off x="685800" y="857250"/>
+          <a:ext cx="2857899" cy="4105848"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2452,15 +2501,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>386954</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>21323</xdr:rowOff>
+      <xdr:colOff>19051</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>137819</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2489,8 +2538,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="684610" y="3280173"/>
-          <a:ext cx="1756172" cy="1575088"/>
+          <a:off x="704851" y="5162550"/>
+          <a:ext cx="3409949" cy="3033419"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2502,15 +2551,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>153329</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>88281</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>464634</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>134744</xdr:rowOff>
+      <xdr:colOff>248579</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>78756</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2525,8 +2574,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="840988" y="2838915"/>
-          <a:ext cx="311305" cy="218378"/>
+          <a:off x="934379" y="4536456"/>
+          <a:ext cx="665821" cy="416544"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2570,15 +2619,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>283426</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>51110</xdr:rowOff>
+      <xdr:colOff>588226</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>60635</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>288073</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>83634</xdr:rowOff>
+      <xdr:colOff>592873</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>93159</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2593,8 +2642,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="971085" y="3145573"/>
-          <a:ext cx="4647" cy="892098"/>
+          <a:off x="1274026" y="5032685"/>
+          <a:ext cx="4647" cy="889774"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2625,16 +2674,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>46464</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>9292</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>367061</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>13939</xdr:rowOff>
+      <xdr:colOff>84564</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>95017</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2649,8 +2698,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1421781" y="4822902"/>
-          <a:ext cx="1008256" cy="4647"/>
+          <a:off x="2141964" y="8153167"/>
+          <a:ext cx="1887111" cy="9758"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2680,23 +2729,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>684609</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>172640</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>669487</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>148828</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>86482</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="図 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2FA29F8-FA32-4026-BD41-763D07505C53}"/>
+        <xdr:cNvPr id="20" name="図 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0AB280C8-A2F0-4A7B-8246-431C7A4984BA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2705,7 +2754,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2718,8 +2767,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="684609" y="5351859"/>
-          <a:ext cx="4092534" cy="3429000"/>
+          <a:off x="685800" y="8743950"/>
+          <a:ext cx="10058400" cy="1629532"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2735,23 +2784,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>684609</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>160</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>262356</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>107701</xdr:rowOff>
+      <xdr:colOff>562436</xdr:colOff>
+      <xdr:row>182</xdr:row>
+      <xdr:rowOff>114842</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="33" name="図 32">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF101071-CD91-4E3B-BA53-28D44F812F2A}"/>
+        <xdr:cNvPr id="60" name="図 59">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C945990D-522A-4F31-8685-22A076940604}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2773,8 +2822,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="684609" y="863203"/>
-          <a:ext cx="3000794" cy="3905795"/>
+          <a:off x="685800" y="27432000"/>
+          <a:ext cx="3305636" cy="3886742"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2786,22 +2835,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>5434</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>4887</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>642937</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>56826</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>131</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>133751</xdr:colOff>
+      <xdr:row>156</xdr:row>
+      <xdr:rowOff>48230</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{736CB2D9-39B1-45BB-BEE5-7248CE18DE77}"/>
+        <xdr:cNvPr id="55" name="図 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24727094-1C38-41DA-AFE3-94BDD13FD974}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2823,8 +2872,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="690043" y="5011465"/>
-          <a:ext cx="2691332" cy="1605705"/>
+          <a:off x="685800" y="22459950"/>
+          <a:ext cx="2876951" cy="4334480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2833,18 +2882,268 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>105173</xdr:colOff>
+      <xdr:row>129</xdr:row>
+      <xdr:rowOff>29153</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="53" name="図 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6005E514-FAC9-4987-A170-0983150881B9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="18002250"/>
+          <a:ext cx="2848373" cy="4143953"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>238541</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>38704</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="50" name="図 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C238642A-6467-489A-94DB-A65E966B5F61}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="13030200"/>
+          <a:ext cx="2981741" cy="4324954"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>152804</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>133919</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="48" name="図 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F521EA8-6DAE-47BF-BB82-2444875B5C25}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="8743950"/>
+          <a:ext cx="2896004" cy="4077269"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>263318</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="44" name="図 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{64C454A5-FFFF-4FC2-850E-31D8DFC8A1CB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="857250"/>
+          <a:ext cx="3006518" cy="4124325"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>14959</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>4887</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>34151</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{736CB2D9-39B1-45BB-BEE5-7248CE18DE77}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="700759" y="5319837"/>
+          <a:ext cx="4819792" cy="2852613"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>286008</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>72576</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>381258</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>44001</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>248736</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>60567</xdr:rowOff>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2859,8 +3158,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1750477" y="4360017"/>
-          <a:ext cx="552087" cy="361847"/>
+          <a:off x="971808" y="4530276"/>
+          <a:ext cx="609342" cy="422724"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2903,16 +3202,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>29765</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>386953</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>41672</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>58340</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2926,9 +3225,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1750219" y="4863703"/>
-          <a:ext cx="5953" cy="1047750"/>
+        <a:xfrm flipH="1">
+          <a:off x="1228725" y="5201840"/>
+          <a:ext cx="9525" cy="1837135"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2957,118 +3256,18 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>5953</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>148829</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>23271</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>100355</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="図 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D19AD40-2190-429E-B4AB-026DFE8E836A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="690562" y="13787438"/>
-          <a:ext cx="4124975" cy="2713776"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>17859</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>11907</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>658631</xdr:colOff>
-      <xdr:row>115</xdr:row>
-      <xdr:rowOff>111558</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="図 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35A303EE-84F0-4C35-AC73-1F948475C2A8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="702468" y="16758048"/>
-          <a:ext cx="2009991" cy="3207182"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
+      <xdr:colOff>233361</xdr:colOff>
+      <xdr:row>126</xdr:row>
+      <xdr:rowOff>79771</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>23812</xdr:colOff>
-      <xdr:row>93</xdr:row>
-      <xdr:rowOff>136921</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>422672</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>71438</xdr:rowOff>
+      <xdr:colOff>142874</xdr:colOff>
+      <xdr:row>129</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3083,8 +3282,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1393031" y="16192499"/>
-          <a:ext cx="398860" cy="279798"/>
+          <a:off x="919161" y="21682471"/>
+          <a:ext cx="595313" cy="463154"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3127,16 +3326,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>279796</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>47624</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>291703</xdr:colOff>
-      <xdr:row>102</xdr:row>
-      <xdr:rowOff>89296</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>129</xdr:row>
+      <xdr:rowOff>114299</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>575071</xdr:colOff>
+      <xdr:row>136</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3150,9 +3349,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1649015" y="16621124"/>
-          <a:ext cx="11907" cy="1077516"/>
+        <a:xfrm flipH="1">
+          <a:off x="1257300" y="22231349"/>
+          <a:ext cx="3571" cy="1238251"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3183,16 +3382,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>398859</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>53578</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>595312</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>59531</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>589359</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>129778</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3206,9 +3405,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1768078" y="6613922"/>
-          <a:ext cx="1565672" cy="5953"/>
+        <a:xfrm flipV="1">
+          <a:off x="2646759" y="8181975"/>
+          <a:ext cx="2715816" cy="5953"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -3236,118 +3435,18 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>627277</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>154781</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="21" name="図 20">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91E36622-7338-44C7-A25C-D4F693470D86}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="684610" y="7250906"/>
-          <a:ext cx="3365714" cy="2226469"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>684609</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>297656</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>153646</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="23" name="図 22">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE492E23-4AF9-4AEF-9E45-B697C7DACC0E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="684609" y="9667876"/>
-          <a:ext cx="3036094" cy="3606458"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>541735</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>29767</xdr:rowOff>
+      <xdr:colOff>284560</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>58342</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>212758</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>89298</xdr:rowOff>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3362,8 +3461,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1226344" y="9179720"/>
-          <a:ext cx="355633" cy="232172"/>
+          <a:off x="970360" y="12402742"/>
+          <a:ext cx="639365" cy="398858"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3406,16 +3505,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>11906</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>154781</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>17859</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>166687</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>97631</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>592931</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3429,9 +3528,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1381125" y="9477375"/>
-          <a:ext cx="5953" cy="1047750"/>
+        <a:xfrm flipH="1">
+          <a:off x="1266825" y="12956381"/>
+          <a:ext cx="11906" cy="1635919"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3462,66 +3561,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>119</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>577453</xdr:colOff>
-      <xdr:row>136</xdr:row>
-      <xdr:rowOff>170762</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="35" name="図 34">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2B2220C-2D48-4674-A3E0-E37798778E74}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="684610" y="20544235"/>
-          <a:ext cx="2631281" cy="3105652"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>138</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>631032</xdr:colOff>
-      <xdr:row>149</xdr:row>
-      <xdr:rowOff>166676</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>666751</xdr:colOff>
+      <xdr:row>183</xdr:row>
+      <xdr:rowOff>161924</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>41113</xdr:colOff>
+      <xdr:row>198</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3550,8 +3599,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="684610" y="23824406"/>
-          <a:ext cx="4054078" cy="2065723"/>
+          <a:off x="666751" y="31537274"/>
+          <a:ext cx="4860762" cy="2457451"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3562,23 +3611,78 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>547688</xdr:colOff>
-      <xdr:row>134</xdr:row>
-      <xdr:rowOff>154781</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>363140</xdr:colOff>
-      <xdr:row>136</xdr:row>
-      <xdr:rowOff>113109</xdr:rowOff>
+      <xdr:colOff>642937</xdr:colOff>
+      <xdr:row>198</xdr:row>
+      <xdr:rowOff>5953</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>198</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="42" name="直線コネクタ 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B93B92B2-844D-455F-A80C-8BE09B9BFFBA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2014537" y="33953053"/>
+          <a:ext cx="3214688" cy="13097"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>179</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>614363</xdr:colOff>
+      <xdr:row>182</xdr:row>
+      <xdr:rowOff>110729</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="38" name="正方形/長方形 37">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6261BA6B-73E8-45EB-A5DD-8E4A14D5A915}"/>
+        <xdr:cNvPr id="61" name="正方形/長方形 60">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9DFE7ED8-458D-4EA5-B47C-76DC0546E704}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3586,8 +3690,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1232297" y="23288625"/>
-          <a:ext cx="500062" cy="303609"/>
+          <a:off x="1390650" y="30851475"/>
+          <a:ext cx="595313" cy="463154"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3631,31 +3735,31 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>137</xdr:row>
-      <xdr:rowOff>53578</xdr:rowOff>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>183</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>144</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:colOff>384571</xdr:colOff>
+      <xdr:row>190</xdr:row>
+      <xdr:rowOff>66676</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="40" name="直線矢印コネクタ 39">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B57C1D4-86AA-45AF-BD62-A8F808422D98}"/>
+        <xdr:cNvPr id="62" name="直線矢印コネクタ 61">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{623264EE-0352-422E-BC33-08F27E49B8E4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1416844" y="23705344"/>
-          <a:ext cx="0" cy="1202531"/>
+        <a:xfrm flipH="1">
+          <a:off x="1752600" y="31403925"/>
+          <a:ext cx="3571" cy="1238251"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3684,61 +3788,6 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>547687</xdr:colOff>
-      <xdr:row>149</xdr:row>
-      <xdr:rowOff>148828</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>535781</xdr:colOff>
-      <xdr:row>149</xdr:row>
-      <xdr:rowOff>154781</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="42" name="直線コネクタ 41">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B93B92B2-844D-455F-A80C-8BE09B9BFFBA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1916906" y="25872281"/>
-          <a:ext cx="2726531" cy="5953"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3748,21 +3797,21 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>556460</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>7481</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>467173</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>162354</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{548A6A45-CAAF-4F99-AA11-9BA8207A05B5}"/>
+        <xdr:cNvPr id="24" name="図 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4B7FCEDC-ADAD-41A3-82E1-F21F3C8CB445}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3784,8 +3833,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="686803" y="852237"/>
-          <a:ext cx="1930065" cy="2393744"/>
+          <a:off x="685800" y="5314950"/>
+          <a:ext cx="3210373" cy="3077004"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3794,18 +3843,68 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>267120</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>76785</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="図 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8852C8C0-87F7-4106-AE7A-B30BD5EABAD9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="857250"/>
+          <a:ext cx="3010320" cy="4191585"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>631658</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>45119</xdr:rowOff>
+      <xdr:colOff>203033</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>35593</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>300790</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>125329</xdr:rowOff>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3820,8 +3919,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1318461" y="2942724"/>
-          <a:ext cx="355934" cy="250658"/>
+          <a:off x="888833" y="4493293"/>
+          <a:ext cx="701842" cy="488281"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3862,68 +3961,18 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>684609</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>23813</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>434578</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>162479</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="図 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{777B70A6-D838-495A-BA2F-E8E1BD84DA3F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="684609" y="3649266"/>
-          <a:ext cx="2488407" cy="1865072"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>65171</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>65171</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>75199</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>5013</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>531896</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>103271</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>541924</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>43113</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3938,8 +3987,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="1438776" y="3303671"/>
-          <a:ext cx="10028" cy="1814763"/>
+          <a:off x="1217696" y="5075321"/>
+          <a:ext cx="10028" cy="1825792"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3971,15 +4020,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>453378</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>161048</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>398233</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>166061</xdr:rowOff>
+      <xdr:colOff>624828</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>84848</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3994,8 +4043,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1822597" y="5512907"/>
-          <a:ext cx="1314074" cy="5013"/>
+          <a:off x="1996428" y="8314448"/>
+          <a:ext cx="1842147" cy="877"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -4025,23 +4074,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>684608</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>678655</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>70812</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>60462</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="20" name="図 19">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D865F412-A799-4525-881E-F2B6A3BC1BF8}"/>
+        <xdr:cNvPr id="27" name="図 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E5F5988-0303-4E71-8DCF-4C64B091FC97}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4063,8 +4112,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="684608" y="6042422"/>
-          <a:ext cx="4786313" cy="4214187"/>
+          <a:off x="685800" y="9001125"/>
+          <a:ext cx="10058400" cy="1603512"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5040,22 +5089,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>9095</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>7328</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>78828</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>82512</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82134122-ABAD-4392-BBCA-1DB1470BC3ED}"/>
+        <xdr:cNvPr id="47" name="図 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{856867D3-245F-47CC-B7EB-7711624886E2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5063,7 +5112,7 @@
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
+      <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
@@ -5071,13 +5120,14 @@
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:srcRect r="61726"/>
-        <a:stretch/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="692267" y="861294"/>
-          <a:ext cx="2802423" cy="2896155"/>
+          <a:off x="685800" y="10629900"/>
+          <a:ext cx="10058400" cy="939762"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5088,23 +5138,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>6569</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>463769</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>73373</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>666750</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>162907</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>29153</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="図 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4FC1563-96C0-4E88-8E72-F03096CA45A2}"/>
+        <xdr:cNvPr id="36" name="図 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58F68B67-503C-462F-908D-8D47E4B281F8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5126,8 +5176,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="689741" y="8939705"/>
-          <a:ext cx="10021614" cy="566703"/>
+          <a:off x="666750" y="1028700"/>
+          <a:ext cx="7039957" cy="4143953"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5139,15 +5189,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>674076</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>7325</xdr:rowOff>
+      <xdr:colOff>178776</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>121624</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>454268</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>109903</xdr:rowOff>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>38099</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5162,8 +5212,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1362807" y="3377710"/>
-          <a:ext cx="468923" cy="271097"/>
+          <a:off x="864576" y="4750774"/>
+          <a:ext cx="640374" cy="430825"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -5206,41 +5256,40 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>271422</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>117092</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>177362</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>36635</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>39414</xdr:rowOff>
+      <xdr:colOff>621013</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123660</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="8" name="直線矢印コネクタ 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{588190D4-AC74-473C-B5BD-4FD78C7BCB3E}"/>
+        <xdr:cNvPr id="19" name="直線コネクタ 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{732CC1B4-01CB-48F9-A011-0FF678C78730}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="1543707" y="3794083"/>
-          <a:ext cx="13138" cy="1369124"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
+        <a:xfrm flipV="1">
+          <a:off x="957222" y="7660892"/>
+          <a:ext cx="1035391" cy="6568"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
           <a:avLst/>
         </a:prstGeom>
         <a:ln w="38100">
           <a:solidFill>
             <a:srgbClr val="FF0000"/>
           </a:solidFill>
-          <a:tailEnd type="triangle"/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -5262,23 +5311,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>683172</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>190547</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>95944</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>19051</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>510926</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="21" name="図 20">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82A34E64-F4E4-485B-BC7C-B1F8F1125485}"/>
+        <xdr:cNvPr id="24" name="図 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D28E90D2-31AE-4121-BA1E-EF0DACC92149}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5300,8 +5349,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="683172" y="9906000"/>
-          <a:ext cx="9754961" cy="266737"/>
+          <a:off x="8220075" y="1047751"/>
+          <a:ext cx="6006851" cy="8086724"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5310,385 +5359,25 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>684609</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>303609</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>16074</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="23" name="図 22">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74771E99-EF13-45CE-BC21-557723F76BEF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="684609" y="3970735"/>
-          <a:ext cx="3042047" cy="2087761"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>242847</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>155192</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>592438</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>161760</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="19" name="直線コネクタ 18">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{732CC1B4-01CB-48F9-A011-0FF678C78730}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="927456" y="4816489"/>
-          <a:ext cx="1034201" cy="6568"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>314739</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>173402</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="24" name="図 23">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D28E90D2-31AE-4121-BA1E-EF0DACC92149}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4124739" y="4000501"/>
-          <a:ext cx="3064565" cy="4173901"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>684609</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>20180</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>29766</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F34AE636-6C80-4CF7-A6A8-352105D70480}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="684609" y="863204"/>
-          <a:ext cx="4127837" cy="2446734"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>11906</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>17858</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>672703</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>9017</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C04F5FB7-6079-4492-BBF7-9AA151F9C436}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="696515" y="3470671"/>
-          <a:ext cx="4083844" cy="2926049"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:colOff>20514</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>102577</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>466725</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>4334</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="図 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F59BEFCE-3634-441F-A425-B620EA713CA0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="695325" y="15230475"/>
-          <a:ext cx="10058400" cy="242459"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>476250</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>130523</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="図 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA456FA6-3879-461C-B092-9F309A452DF5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="704850" y="14344650"/>
-          <a:ext cx="10058400" cy="568673"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>117872</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>59530</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>470297</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:colOff>380999</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="正方形/長方形 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{514786E5-8A73-41B9-899C-DB0BC60D61A2}"/>
+        <xdr:cNvPr id="28" name="正方形/長方形 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B59CAC07-C0C3-4545-830F-F8AC09F2799B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5696,8 +5385,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="802481" y="2994421"/>
-          <a:ext cx="352425" cy="275035"/>
+          <a:off x="706314" y="11246827"/>
+          <a:ext cx="9961685" cy="287948"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5740,23 +5429,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>29766</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>23813</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>109929</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>86694</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>162594</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="図 15">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF376C01-4212-48A5-B4BD-69430F0E6F28}"/>
+        <xdr:cNvPr id="45" name="図 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{821D1B50-E628-48E1-A4D1-95A08AF60411}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5765,7 +5454,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -5778,8 +5467,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5476876" y="3482579"/>
-          <a:ext cx="4131468" cy="5604663"/>
+          <a:off x="685800" y="5486400"/>
+          <a:ext cx="6944694" cy="4791744"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5791,22 +5480,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>317897</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>90488</xdr:rowOff>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>8060</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>327422</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>119063</xdr:rowOff>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="14" name="直線矢印コネクタ 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FDEEA49-A986-445E-A562-EC360F58FF36}"/>
+        <xdr:cNvPr id="8" name="直線矢印コネクタ 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{588190D4-AC74-473C-B5BD-4FD78C7BCB3E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5814,8 +5503,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1002506" y="3370660"/>
-          <a:ext cx="9525" cy="1064419"/>
+          <a:off x="1190625" y="5151560"/>
+          <a:ext cx="9525" cy="1792165"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -5844,85 +5533,30 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>184547</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>41672</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>208359</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>41672</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="4" name="直線コネクタ 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C76733D-880D-4031-B357-9C3069494AA8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="869156" y="4702969"/>
-          <a:ext cx="708422" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>684609</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>482203</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>125110</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>58064</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="図 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C303A514-C0E4-4BE5-A22C-1E623BB385F5}"/>
+        <xdr:cNvPr id="33" name="図 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91DE12DC-D5F0-4849-95C0-A5F8B7EE962D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5944,8 +5578,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="684609" y="863204"/>
-          <a:ext cx="2536032" cy="3060000"/>
+          <a:off x="685800" y="9772650"/>
+          <a:ext cx="10058400" cy="1258214"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5957,22 +5591,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>3411</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>12394</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>296432</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>457</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>152804</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>86335</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BF903D9-2454-455A-BA5E-5C8AC82F646B}"/>
+        <xdr:cNvPr id="28" name="図 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{735468B1-A3F2-488B-B8AE-F20D4A4A617D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5994,8 +5628,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="688020" y="4155769"/>
-          <a:ext cx="5085287" cy="3268235"/>
+          <a:off x="685800" y="4800600"/>
+          <a:ext cx="2896004" cy="4372585"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6007,22 +5641,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>17860</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>157933</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>41672</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>648</xdr:rowOff>
+      <xdr:colOff>8333</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>133351</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>304854</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92D08D4C-C321-43D0-B28C-7D80F795A0F3}"/>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F34AE636-6C80-4CF7-A6A8-352105D70480}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6044,8 +5678,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="702469" y="7926761"/>
-          <a:ext cx="4816078" cy="3813450"/>
+          <a:off x="694133" y="819151"/>
+          <a:ext cx="6468721" cy="3800474"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6056,23 +5690,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>232172</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>69055</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>59531</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>107156</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>541217</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>81377</xdr:rowOff>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="正方形/長方形 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F7099CF-BA73-492A-95C6-2433C92D86CF}"/>
+        <xdr:cNvPr id="10" name="正方形/長方形 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{514786E5-8A73-41B9-899C-DB0BC60D61A2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6080,8 +5714,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1428750" y="3559969"/>
-          <a:ext cx="481686" cy="319502"/>
+          <a:off x="917972" y="4183855"/>
+          <a:ext cx="529828" cy="311945"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6124,40 +5758,41 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>598793</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>53577</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>482203</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>53852</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>157163</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>489348</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="6" name="直線コネクタ 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FAC2EADB-A000-4830-857E-FC9DE6392111}"/>
+        <xdr:cNvPr id="14" name="直線矢印コネクタ 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FDEEA49-A986-445E-A562-EC360F58FF36}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="1968012" y="5750718"/>
-          <a:ext cx="1252629" cy="275"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
+        <a:xfrm flipH="1">
+          <a:off x="1162050" y="4614863"/>
+          <a:ext cx="13098" cy="1757362"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
           <a:avLst/>
         </a:prstGeom>
         <a:ln w="38100">
           <a:solidFill>
             <a:srgbClr val="FF0000"/>
           </a:solidFill>
+          <a:tailEnd type="triangle"/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -6179,32 +5814,32 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>566739</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>154781</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>446484</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>158354</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="7" name="直線コネクタ 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B87D2B2-E891-4D04-AD7A-E712E064E54C}"/>
+        <xdr:cNvPr id="4" name="直線コネクタ 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C76733D-880D-4031-B357-9C3069494AA8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="1935958" y="6715125"/>
-          <a:ext cx="1248964" cy="3573"/>
+        <a:xfrm>
+          <a:off x="1019175" y="6905625"/>
+          <a:ext cx="1076325" cy="9525"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -6234,23 +5869,264 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="34" name="正方形/長方形 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70F31340-0D52-4ABE-BCE7-A3913490D71D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="695325" y="10658475"/>
+          <a:ext cx="9972675" cy="276225"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent2"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>684609</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>657225</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>126281</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C303A514-C0E4-4BE5-A22C-1E623BB385F5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="684609" y="857251"/>
+          <a:ext cx="3401616" cy="4069630"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>679686</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>21919</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>628650</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>150374</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BF903D9-2454-455A-BA5E-5C8AC82F646B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="679686" y="5165419"/>
+          <a:ext cx="6121164" cy="3900355"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>619124</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>29765</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>464342</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>32146</xdr:rowOff>
+      <xdr:colOff>335755</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>2381</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>257174</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F7099CF-BA73-492A-95C6-2433C92D86CF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1707355" y="4460081"/>
+          <a:ext cx="607219" cy="369094"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent2"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>265418</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>167877</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>148828</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>168152</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="8" name="直線コネクタ 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B78B429-A837-4F1B-B153-4761CC78A1EB}"/>
+        <xdr:cNvPr id="6" name="直線コネクタ 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FAC2EADB-A000-4830-857E-FC9DE6392111}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6258,8 +6134,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="1988343" y="6244828"/>
-          <a:ext cx="1214437" cy="2381"/>
+          <a:off x="2322818" y="7025877"/>
+          <a:ext cx="1255010" cy="275"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -6289,16 +6165,126 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>333376</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>172640</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>339328</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>17859</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>271464</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>135731</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>151209</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>139304</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="直線コネクタ 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B87D2B2-E891-4D04-AD7A-E712E064E54C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="2328864" y="8193881"/>
+          <a:ext cx="1251345" cy="3573"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>304799</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>58340</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>150017</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>60721</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="8" name="直線コネクタ 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B78B429-A837-4F1B-B153-4761CC78A1EB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="2362199" y="7602140"/>
+          <a:ext cx="1216818" cy="2381"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>19051</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>20240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -6313,8 +6299,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1702595" y="3970734"/>
-          <a:ext cx="5952" cy="1571625"/>
+          <a:off x="2076451" y="4992290"/>
+          <a:ext cx="19049" cy="2027635"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -6343,6 +6329,56 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>58064</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="28" name="図 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6AE57657-9D42-4606-AEDA-14F817433572}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="9601200"/>
+          <a:ext cx="10058400" cy="1258214"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -6401,15 +6437,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>5253</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>4553</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>244552</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>70757</xdr:rowOff>
+      <xdr:colOff>14778</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>156953</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>1814</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6438,8 +6474,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8234853" y="2791296"/>
-          <a:ext cx="2982499" cy="4072147"/>
+          <a:off x="8244378" y="2728703"/>
+          <a:ext cx="5473436" cy="7358272"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7444,22 +7480,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>10820</xdr:colOff>
-      <xdr:row>200</xdr:row>
-      <xdr:rowOff>156884</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>416719</xdr:colOff>
-      <xdr:row>207</xdr:row>
-      <xdr:rowOff>92633</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>274</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>344327</xdr:colOff>
+      <xdr:row>285</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="55" name="図 54">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBDDEE7D-30B2-4B24-99F6-8BDFEF364904}"/>
+        <xdr:cNvPr id="124" name="図 123">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{686F4342-43F5-4E0A-B929-16667042243D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7467,7 +7503,7 @@
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
+      <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
@@ -7475,13 +7511,14 @@
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:srcRect b="59495"/>
-        <a:stretch/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="695429" y="34685009"/>
-          <a:ext cx="4513556" cy="1144233"/>
+          <a:off x="685800" y="46977300"/>
+          <a:ext cx="7202327" cy="2028825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7493,22 +7530,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>5954</xdr:colOff>
-      <xdr:row>142</xdr:row>
-      <xdr:rowOff>166687</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>476251</xdr:colOff>
-      <xdr:row>159</xdr:row>
-      <xdr:rowOff>104348</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>244</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>201010</xdr:colOff>
+      <xdr:row>268</xdr:row>
+      <xdr:rowOff>29153</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="47" name="図 46">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36103C72-5324-4D3E-AF96-C7093BD4C902}"/>
+        <xdr:cNvPr id="116" name="図 115">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D454649B-CF4E-471D-9737-440D146B70D1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7530,8 +7567,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="690563" y="24681656"/>
-          <a:ext cx="3893344" cy="2872551"/>
+          <a:off x="685800" y="41833800"/>
+          <a:ext cx="7059010" cy="4143953"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7542,23 +7579,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>684609</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>11907</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>181862</xdr:colOff>
-      <xdr:row>134</xdr:row>
-      <xdr:rowOff>31606</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>225</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>48015</xdr:colOff>
+      <xdr:row>240</xdr:row>
+      <xdr:rowOff>38464</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="図 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E680A21C-6A7B-48BB-809A-F9999AAA0EA8}"/>
+        <xdr:cNvPr id="112" name="図 111">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ABB93F8A-DB9F-4542-9150-A7781204B321}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7567,7 +7604,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -7580,8 +7617,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="684609" y="18484454"/>
-          <a:ext cx="6343347" cy="4680996"/>
+          <a:off x="685800" y="38576250"/>
+          <a:ext cx="2791215" cy="2610214"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7593,22 +7630,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>15139</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>5444</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>500743</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>47696</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>196</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>143278</xdr:colOff>
+      <xdr:row>224</xdr:row>
+      <xdr:rowOff>67354</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B2875B9-3E5B-4036-B3DE-E87151C2986E}"/>
+        <xdr:cNvPr id="110" name="図 109">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A579A15F-D9A0-4A26-AFF6-9C05D8C5F731}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7617,7 +7654,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -7630,8 +7667,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="700939" y="1921330"/>
-          <a:ext cx="3914604" cy="2306480"/>
+          <a:off x="685800" y="33604200"/>
+          <a:ext cx="2886478" cy="4867954"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7643,72 +7680,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>9016</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>165680</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>681221</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>27214</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>157</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>457647</xdr:colOff>
+      <xdr:row>182</xdr:row>
+      <xdr:rowOff>67283</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62A9540C-E8E4-4162-B9FF-E6E1E51D586C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="694816" y="4519966"/>
-          <a:ext cx="4101205" cy="2648277"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>44106</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>164224</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>522514</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>5353</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="図 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6B77559-B4D3-4944-B491-39569172638A}"/>
+        <xdr:cNvPr id="105" name="図 104">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69919B99-F3C9-4D82-BDFF-8320F88BC446}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7730,8 +7717,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="729906" y="7827767"/>
-          <a:ext cx="4593208" cy="711986"/>
+          <a:off x="685800" y="26917650"/>
+          <a:ext cx="3200847" cy="4353533"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7743,22 +7730,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>18018</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>1126</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>16565</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>86390</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>67067</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>10125</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="図 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF21DB78-634B-4560-8A2B-887B3B9B3C66}"/>
+        <xdr:cNvPr id="95" name="図 94">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90206A5B-BC47-4953-90F8-0C52966D8AD4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7767,7 +7754,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -7780,8 +7767,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="705475" y="9045735"/>
-          <a:ext cx="3435829" cy="2346416"/>
+          <a:off x="685800" y="16116300"/>
+          <a:ext cx="2810267" cy="4296375"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7792,23 +7779,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>681795</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>2057</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>29308</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>9184</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>158953</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="図 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4889C18-85F5-4E63-B51F-090671400A56}"/>
+        <xdr:cNvPr id="91" name="図 90">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{948A97CF-276C-44A3-A51D-4EC58D5E550C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7817,7 +7804,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -7830,8 +7817,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="681795" y="11124326"/>
-          <a:ext cx="3479898" cy="2534916"/>
+          <a:off x="685800" y="9944100"/>
+          <a:ext cx="10058400" cy="1187653"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7843,22 +7830,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>675082</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>20240</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>404811</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>104364</xdr:rowOff>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>76595</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>48229</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="図 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E973615-A504-4EDB-9E20-9390BD5EE023}"/>
+        <xdr:cNvPr id="87" name="図 86">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A02AD5E2-B21D-4AD3-B296-4130C559E461}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7880,8 +7867,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="675082" y="14694693"/>
-          <a:ext cx="8629651" cy="256765"/>
+          <a:off x="676275" y="5153025"/>
+          <a:ext cx="2829320" cy="4324954"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7893,22 +7880,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>4580</xdr:colOff>
-      <xdr:row>89</xdr:row>
-      <xdr:rowOff>159819</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>21981</xdr:colOff>
-      <xdr:row>105</xdr:row>
-      <xdr:rowOff>80537</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>9909</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>124393</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D90EBD02-69B9-4518-AF44-81A4A37565A2}"/>
+        <xdr:cNvPr id="84" name="図 83">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{948C7678-FBE6-4323-89F4-CD86C253C902}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7930,8 +7917,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="693311" y="15158031"/>
-          <a:ext cx="4149785" cy="2617025"/>
+          <a:off x="685800" y="857250"/>
+          <a:ext cx="2753109" cy="4067743"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7940,368 +7927,18 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>5952</xdr:colOff>
-      <xdr:row>138</xdr:row>
-      <xdr:rowOff>11905</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>142874</xdr:colOff>
-      <xdr:row>139</xdr:row>
-      <xdr:rowOff>152745</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C425462F-E4C0-4589-A04E-ED7D9EFBF7A4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="690561" y="23836311"/>
-          <a:ext cx="10406063" cy="313481"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>13125</xdr:colOff>
-      <xdr:row>161</xdr:row>
-      <xdr:rowOff>27213</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>364671</xdr:colOff>
-      <xdr:row>170</xdr:row>
-      <xdr:rowOff>121072</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="図 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{252B817D-1247-4F5A-9AB5-83CB6DB2D361}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="698925" y="28068813"/>
-          <a:ext cx="3780546" cy="1661402"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>10886</xdr:colOff>
-      <xdr:row>174</xdr:row>
-      <xdr:rowOff>28644</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>157843</xdr:colOff>
-      <xdr:row>185</xdr:row>
-      <xdr:rowOff>30235</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="図 15">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DAB773E-FAC7-4F8B-91CB-CBE466BC9EF1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="696686" y="30334473"/>
-          <a:ext cx="2890157" cy="1917476"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>2840</xdr:colOff>
-      <xdr:row>186</xdr:row>
-      <xdr:rowOff>162103</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>272144</xdr:colOff>
-      <xdr:row>197</xdr:row>
-      <xdr:rowOff>144082</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="図 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE562746-06A8-4C7B-B9B3-3CE868B9CEA2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="688640" y="32557989"/>
-          <a:ext cx="3012504" cy="1897864"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>683655</xdr:colOff>
-      <xdr:row>208</xdr:row>
-      <xdr:rowOff>163997</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>303609</xdr:colOff>
-      <xdr:row>219</xdr:row>
-      <xdr:rowOff>93346</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="20" name="図 19">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1ABF22F4-4B3D-41BB-85BC-647FCA213946}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="683655" y="36073247"/>
-          <a:ext cx="4412220" cy="1828396"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>683173</xdr:colOff>
-      <xdr:row>222</xdr:row>
-      <xdr:rowOff>140352</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>291354</xdr:colOff>
-      <xdr:row>238</xdr:row>
-      <xdr:rowOff>107995</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="22" name="図 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4144EA69-3B4E-4A52-9E08-AF29FF513F73}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="683173" y="37455940"/>
-          <a:ext cx="3709534" cy="2657055"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>7425</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>7139</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>220624</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>157843</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="24" name="図 23">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7492C659-B607-471E-A51D-90192FE9B58F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="693225" y="1052168"/>
-          <a:ext cx="5699599" cy="324875"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>47110</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>568684</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>136071</xdr:rowOff>
+      <xdr:colOff>209549</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>123310</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>66674</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -8316,8 +7953,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="876300" y="3878881"/>
-          <a:ext cx="378184" cy="263133"/>
+          <a:off x="895349" y="4581010"/>
+          <a:ext cx="542925" cy="333890"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8361,15 +7998,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>337457</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>45795</xdr:rowOff>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>7695</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>348718</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>97971</xdr:rowOff>
+      <xdr:colOff>463019</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -8384,8 +8021,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="1023257" y="4225909"/>
-          <a:ext cx="11261" cy="1097205"/>
+          <a:off x="1143000" y="4979745"/>
+          <a:ext cx="5819" cy="1116255"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -8417,15 +8054,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>239486</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>130629</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>108857</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>130629</xdr:rowOff>
+      <xdr:colOff>229961</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>83004</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -8439,9 +8076,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="925286" y="5529943"/>
-          <a:ext cx="555171" cy="0"/>
+        <a:xfrm flipV="1">
+          <a:off x="915761" y="7277100"/>
+          <a:ext cx="1151164" cy="6804"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -8472,22 +8109,354 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>375556</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>70757</xdr:rowOff>
+      <xdr:colOff>504074</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>129878</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="33" name="直線矢印コネクタ 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D09A7A6-2AEC-44CA-9D3C-AE98FC5628B0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1189874" y="15903278"/>
+          <a:ext cx="751" cy="1679872"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>293875</xdr:colOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>70381</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>163286</xdr:rowOff>
+      <xdr:colOff>657225</xdr:colOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>62232</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="37" name="直線コネクタ 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{461C6EB9-827F-4198-A1AA-FE6EBCB89C5D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="979675" y="18230850"/>
+          <a:ext cx="1049150" cy="5082"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>570308</xdr:colOff>
+      <xdr:row>156</xdr:row>
+      <xdr:rowOff>80962</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>576261</xdr:colOff>
+      <xdr:row>165</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="40" name="直線矢印コネクタ 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3AE5B9B9-90EA-48E5-9B9F-F10716C5117B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1256108" y="26827162"/>
+          <a:ext cx="5953" cy="1566863"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>9524</xdr:colOff>
+      <xdr:row>179</xdr:row>
+      <xdr:rowOff>38102</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>415528</xdr:colOff>
+      <xdr:row>179</xdr:row>
+      <xdr:rowOff>38102</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="42" name="直線コネクタ 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F38C65BA-9D4E-4066-81B0-6CC6B7BE6B7B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2066924" y="30727652"/>
+          <a:ext cx="1777604" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>659605</xdr:colOff>
+      <xdr:row>174</xdr:row>
+      <xdr:rowOff>158353</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>379809</xdr:colOff>
+      <xdr:row>174</xdr:row>
+      <xdr:rowOff>158353</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="43" name="直線コネクタ 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7DC5B5E-E7D0-436C-B073-11E0AE5CA586}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2031205" y="29990653"/>
+          <a:ext cx="1777604" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>665560</xdr:colOff>
+      <xdr:row>170</xdr:row>
+      <xdr:rowOff>110727</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>385764</xdr:colOff>
+      <xdr:row>170</xdr:row>
+      <xdr:rowOff>110727</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="44" name="直線コネクタ 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AA4FEA0-0FAF-4590-988E-6C86A8611A8E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2037160" y="29257227"/>
+          <a:ext cx="1777604" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>136185</xdr:colOff>
+      <xdr:row>221</xdr:row>
+      <xdr:rowOff>101057</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>342901</xdr:colOff>
+      <xdr:row>223</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="31" name="正方形/長方形 30">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB14B386-CCFF-4D4F-AEE9-F89CA36FC6AC}"/>
+        <xdr:cNvPr id="45" name="正方形/長方形 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03A346EF-FDF0-4880-8BE9-5FAEBABBAF4B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8495,8 +8464,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1061356" y="11043557"/>
-          <a:ext cx="380625" cy="266700"/>
+          <a:off x="1507785" y="37991507"/>
+          <a:ext cx="892516" cy="403768"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8539,32 +8508,32 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>532649</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>91778</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>541735</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>101203</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>493939</xdr:colOff>
+      <xdr:row>224</xdr:row>
+      <xdr:rowOff>164596</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>503055</xdr:colOff>
+      <xdr:row>231</xdr:row>
+      <xdr:rowOff>77561</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="33" name="直線矢印コネクタ 32">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D09A7A6-2AEC-44CA-9D3C-AE98FC5628B0}"/>
+        <xdr:cNvPr id="46" name="直線矢印コネクタ 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C0924AC-F102-43C9-BA62-7F3CDC65867B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1217258" y="11313419"/>
-          <a:ext cx="9086" cy="872628"/>
+        <a:xfrm flipH="1">
+          <a:off x="1865539" y="38569396"/>
+          <a:ext cx="9116" cy="1113115"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -8595,78 +8564,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>417700</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>154782</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>321468</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>157481</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="37" name="直線コネクタ 36">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{461C6EB9-827F-4198-A1AA-FE6EBCB89C5D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="1102309" y="12412266"/>
-          <a:ext cx="588378" cy="2699"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>672703</xdr:colOff>
-      <xdr:row>103</xdr:row>
-      <xdr:rowOff>17859</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>420004</xdr:colOff>
-      <xdr:row>104</xdr:row>
-      <xdr:rowOff>141847</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>141514</xdr:colOff>
+      <xdr:row>265</xdr:row>
+      <xdr:rowOff>82649</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>268</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="38" name="正方形/長方形 37">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{977103E5-9324-40CD-B7CD-DF6BAD04AD60}"/>
+        <xdr:cNvPr id="48" name="正方形/長方形 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BBCC966-FEBA-431B-98F9-F6DCD946E6F2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8674,8 +8588,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1357312" y="17799843"/>
-          <a:ext cx="431911" cy="296629"/>
+          <a:off x="6999514" y="45516899"/>
+          <a:ext cx="687161" cy="469801"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8718,23 +8632,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>208358</xdr:colOff>
-      <xdr:row>105</xdr:row>
-      <xdr:rowOff>71437</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>214311</xdr:colOff>
-      <xdr:row>114</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>265866</xdr:colOff>
+      <xdr:row>268</xdr:row>
+      <xdr:rowOff>154597</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>273</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="40" name="直線矢印コネクタ 39">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3AE5B9B9-90EA-48E5-9B9F-F10716C5117B}"/>
+        <xdr:cNvPr id="49" name="直線矢印コネクタ 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC490D65-1024-47F0-B1D0-91BAF7283881}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8742,8 +8656,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1577577" y="18198703"/>
-          <a:ext cx="5953" cy="1577578"/>
+          <a:off x="7123866" y="46103197"/>
+          <a:ext cx="834" cy="778853"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -8774,188 +8688,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>523874</xdr:colOff>
-      <xdr:row>127</xdr:row>
-      <xdr:rowOff>95252</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>244078</xdr:colOff>
-      <xdr:row>127</xdr:row>
-      <xdr:rowOff>95252</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="42" name="直線コネクタ 41">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F38C65BA-9D4E-4066-81B0-6CC6B7BE6B7B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2577702" y="22020611"/>
-          <a:ext cx="1774032" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>535780</xdr:colOff>
-      <xdr:row>123</xdr:row>
-      <xdr:rowOff>53578</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>255984</xdr:colOff>
-      <xdr:row>123</xdr:row>
-      <xdr:rowOff>53578</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="43" name="直線コネクタ 42">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7DC5B5E-E7D0-436C-B073-11E0AE5CA586}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2589608" y="21288375"/>
-          <a:ext cx="1774032" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>541735</xdr:colOff>
-      <xdr:row>118</xdr:row>
-      <xdr:rowOff>148827</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>261939</xdr:colOff>
-      <xdr:row>118</xdr:row>
-      <xdr:rowOff>148827</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="44" name="直線コネクタ 43">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AA4FEA0-0FAF-4590-988E-6C86A8611A8E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2595563" y="20520421"/>
-          <a:ext cx="1774032" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>602909</xdr:colOff>
-      <xdr:row>157</xdr:row>
-      <xdr:rowOff>158207</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>348156</xdr:colOff>
-      <xdr:row>159</xdr:row>
-      <xdr:rowOff>39414</xdr:rowOff>
+      <xdr:colOff>285751</xdr:colOff>
+      <xdr:row>275</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>285</xdr:row>
+      <xdr:rowOff>122464</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="45" name="正方形/長方形 44">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03A346EF-FDF0-4880-8BE9-5FAEBABBAF4B}"/>
+        <xdr:cNvPr id="56" name="正方形/長方形 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{182203F5-B829-4AD2-83F5-BE4E36A5D500}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8963,8 +8712,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1286081" y="26972724"/>
-          <a:ext cx="428420" cy="222793"/>
+          <a:off x="1657351" y="47253525"/>
+          <a:ext cx="5895974" cy="1732189"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9007,79 +8756,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>141514</xdr:colOff>
-      <xdr:row>160</xdr:row>
-      <xdr:rowOff>40771</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>150630</xdr:colOff>
-      <xdr:row>166</xdr:row>
-      <xdr:rowOff>125186</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="46" name="直線矢印コネクタ 45">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C0924AC-F102-43C9-BA62-7F3CDC65867B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="1513114" y="27908200"/>
-          <a:ext cx="9116" cy="1129443"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>293914</xdr:colOff>
-      <xdr:row>183</xdr:row>
-      <xdr:rowOff>73125</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>639675</xdr:colOff>
-      <xdr:row>184</xdr:row>
-      <xdr:rowOff>103415</xdr:rowOff>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="48" name="正方形/長方形 47">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BBCC966-FEBA-431B-98F9-F6DCD946E6F2}"/>
+        <xdr:cNvPr id="82" name="正方形/長方形 81">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B67607A7-DE8D-452E-B10C-A847E4ADDC8F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9087,8 +8780,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="979714" y="31946496"/>
-          <a:ext cx="345761" cy="204462"/>
+          <a:off x="762000" y="10487025"/>
+          <a:ext cx="9944100" cy="333375"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9129,81 +8822,75 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>124225</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>67259</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="93" name="図 92">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B0C3D72C-3794-446F-9E0B-2E532F054E50}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="11658600"/>
+          <a:ext cx="2867425" cy="4182059"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>580191</xdr:colOff>
-      <xdr:row>184</xdr:row>
-      <xdr:rowOff>154597</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>583660</xdr:colOff>
-      <xdr:row>187</xdr:row>
-      <xdr:rowOff>48638</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="49" name="直線矢印コネクタ 48">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC490D65-1024-47F0-B1D0-91BAF7283881}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1265180" y="31477661"/>
-          <a:ext cx="3469" cy="404743"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>571499</xdr:colOff>
-      <xdr:row>205</xdr:row>
-      <xdr:rowOff>47624</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>514878</xdr:colOff>
-      <xdr:row>206</xdr:row>
-      <xdr:rowOff>164224</xdr:rowOff>
+      <xdr:colOff>251731</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>108857</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="51" name="正方形/長方形 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79EB807F-1DEF-45F9-8914-8D75BCDE7B3E}"/>
+        <xdr:cNvPr id="31" name="正方形/長方形 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB14B386-CCFF-4D4F-AEE9-F89CA36FC6AC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9211,8 +8898,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3309937" y="35438952"/>
-          <a:ext cx="627988" cy="289241"/>
+          <a:off x="937531" y="15367907"/>
+          <a:ext cx="595994" cy="462643"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9253,81 +8940,75 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>122</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>128</xdr:row>
+      <xdr:rowOff>161555</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="97" name="図 96">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1368C095-2C42-4756-B40E-38CC11D9F789}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="20916900"/>
+          <a:ext cx="10058400" cy="1190255"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>244634</xdr:colOff>
-      <xdr:row>207</xdr:row>
-      <xdr:rowOff>103944</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>247773</xdr:colOff>
-      <xdr:row>215</xdr:row>
-      <xdr:rowOff>82523</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="52" name="直線矢印コネクタ 51">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{126B2741-5D51-4B02-BA16-074CE8593DB3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3667681" y="35840553"/>
-          <a:ext cx="3139" cy="1359704"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>549729</xdr:colOff>
-      <xdr:row>187</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>566057</xdr:colOff>
-      <xdr:row>191</xdr:row>
-      <xdr:rowOff>103414</xdr:rowOff>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>126</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>128</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="56" name="正方形/長方形 55">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{182203F5-B829-4AD2-83F5-BE4E36A5D500}"/>
+        <xdr:cNvPr id="101" name="正方形/長方形 100">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26DFEB05-C513-4F82-9958-90DB03D3FEF3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9335,8 +9016,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1235529" y="32684357"/>
-          <a:ext cx="2073728" cy="685800"/>
+          <a:off x="704850" y="21764625"/>
+          <a:ext cx="9991725" cy="333375"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9377,30 +9058,25 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>683172</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>132</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>675409</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>52433</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>124225</xdr:colOff>
+      <xdr:row>155</xdr:row>
+      <xdr:rowOff>162498</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BA5CF7E-0AE5-4CFD-9EB1-B4872DB1E2C3}"/>
+        <xdr:cNvPr id="103" name="図 102">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44E77BA4-B67A-4854-B186-D9B15E7C3A11}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9409,7 +9085,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -9422,8 +9098,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="683172" y="865909"/>
-          <a:ext cx="4148601" cy="2303797"/>
+          <a:off x="685800" y="22631400"/>
+          <a:ext cx="2867425" cy="4105848"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9432,75 +9108,25 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>17318</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>60097</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD56E484-7D4F-40E4-93A6-5E0BAAD54F1B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="688731" y="3201866"/>
-          <a:ext cx="4149702" cy="2587885"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>505556</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>84992</xdr:rowOff>
+      <xdr:colOff>263128</xdr:colOff>
+      <xdr:row>153</xdr:row>
+      <xdr:rowOff>122633</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>167052</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>139211</xdr:rowOff>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>155</xdr:row>
+      <xdr:rowOff>142874</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="正方形/長方形 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8544A1FB-93FF-4A1C-A209-493C4546999F}"/>
+        <xdr:cNvPr id="38" name="正方形/長方形 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{977103E5-9324-40CD-B7CD-DF6BAD04AD60}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9508,8 +9134,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1194287" y="2781300"/>
-          <a:ext cx="350227" cy="222738"/>
+          <a:off x="948928" y="26354483"/>
+          <a:ext cx="603647" cy="363141"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9550,18 +9176,409 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>186</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>193</xdr:row>
+      <xdr:rowOff>4800</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="107" name="図 106">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B73C8688-9CAB-4597-9E48-B908B5D284D5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="31889700"/>
+          <a:ext cx="10058400" cy="1204950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>675543</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>67408</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>191</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>193</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="108" name="正方形/長方形 107">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F67DAC8-754D-4397-96CC-4787AA5C1767}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="742950" y="32775525"/>
+          <a:ext cx="10001250" cy="323850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>685068</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>38833</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>289</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>124225</xdr:colOff>
+      <xdr:row>304</xdr:row>
+      <xdr:rowOff>359</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="127" name="図 126">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{089DA33B-DA49-4D05-8527-85FD5C9DE450}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="49549050"/>
+          <a:ext cx="2867425" cy="2572109"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>307</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>312</xdr:row>
+      <xdr:rowOff>60461</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="129" name="図 128">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84E48BF9-97D8-4255-9149-97CED6674838}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="52635150"/>
+          <a:ext cx="10058400" cy="917711"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>171857</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>128484</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="図 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D062D82C-C08E-494D-927E-134400F228C6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="870857"/>
+          <a:ext cx="2915057" cy="4134427"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>665403</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>161924</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD56E484-7D4F-40E4-93A6-5E0BAAD54F1B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="676275" y="5153025"/>
+          <a:ext cx="6161328" cy="3924299"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>324580</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>56417</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>228599</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="正方形/長方形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8544A1FB-93FF-4A1C-A209-493C4546999F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1010380" y="4514117"/>
+          <a:ext cx="589819" cy="372208"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="accent2"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>532668</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>733</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>542193</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>143608</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -9576,8 +9593,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="1364274" y="3100754"/>
-          <a:ext cx="9525" cy="1151060"/>
+          <a:off x="1218468" y="4972783"/>
+          <a:ext cx="9525" cy="1171575"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -9608,16 +9625,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>466724</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>65942</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>36635</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>70338</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>314324</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>361950</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>13188</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -9632,8 +9649,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="1844186" y="4447442"/>
-          <a:ext cx="947372" cy="4396"/>
+          <a:off x="2371724" y="8239125"/>
+          <a:ext cx="1419226" cy="3663"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -9663,16 +9680,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>418367</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>124558</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>43962</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>126756</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>332642</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>31506</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -9686,9 +9703,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="1795829" y="4843096"/>
-          <a:ext cx="1003056" cy="2198"/>
+        <a:xfrm>
+          <a:off x="2390042" y="7060956"/>
+          <a:ext cx="1419958" cy="16119"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -9718,16 +9735,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>386861</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>21981</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>65942</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>25644</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>253511</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>82795</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -9741,9 +9758,9 @@
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="1764323" y="5246077"/>
-          <a:ext cx="1056542" cy="3663"/>
+        <a:xfrm>
+          <a:off x="2310911" y="7626595"/>
+          <a:ext cx="1508614" cy="2930"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -9773,23 +9790,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>681405</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>139213</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>674077</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>117419</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>147867</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="図 16">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{705FA64D-41E5-44C6-9216-361C019C7A15}"/>
+        <xdr:cNvPr id="29" name="図 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF0FCB52-EB18-4683-963E-234A295D2E26}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9798,7 +9815,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -9811,8 +9828,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="681405" y="6374425"/>
-          <a:ext cx="2747595" cy="2000436"/>
+          <a:off x="685800" y="9601200"/>
+          <a:ext cx="10058400" cy="1005117"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9829,15 +9846,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>684609</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>23813</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>165827</xdr:rowOff>
+      <xdr:colOff>646508</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>23812</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>52693</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -9866,8 +9883,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="684609" y="2268141"/>
-          <a:ext cx="3423047" cy="1350499"/>
+          <a:off x="646508" y="3109912"/>
+          <a:ext cx="6949985" cy="2719388"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9879,15 +9896,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>684609</xdr:colOff>
+      <xdr:colOff>684608</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>166687</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>23813</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>25772</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>551007</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -9916,8 +9933,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="684609" y="857250"/>
-          <a:ext cx="3446860" cy="1067569"/>
+          <a:off x="684608" y="852487"/>
+          <a:ext cx="6724399" cy="2062163"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9928,16 +9945,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>122109</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>350708</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>51718</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>127919</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>464633</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>9293</xdr:rowOff>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -9952,8 +9969,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4248060" y="815578"/>
-          <a:ext cx="2405500" cy="569032"/>
+          <a:off x="7208708" y="223168"/>
+          <a:ext cx="2468692" cy="538832"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRoundRectCallout">
           <a:avLst>
@@ -10014,16 +10031,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>29766</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>85484</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>412204</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>50525</xdr:rowOff>
+      <xdr:colOff>267891</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>171209</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>650329</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>136250</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -10038,8 +10055,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2083594" y="3193015"/>
-          <a:ext cx="2436266" cy="482963"/>
+          <a:off x="4382691" y="5314709"/>
+          <a:ext cx="2439838" cy="479391"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRoundRectCallout">
           <a:avLst>
@@ -10450,8 +10467,8 @@
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B5" s="1" t="s">
-        <v>2</v>
+      <c r="B5" s="2" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -10469,16 +10486,16 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B4" s="2" t="s">
-        <v>56</v>
+      <c r="B4" s="3" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B5" s="5"/>
+      <c r="B5" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -10489,35 +10506,45 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0771CA-5847-4081-9CE1-80252A4D320F}">
-  <dimension ref="B2:B146"/>
+  <dimension ref="B2:G153"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B37" s="2" t="s">
-        <v>59</v>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B47" s="3" t="s">
+        <v>46</v>
       </c>
     </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B66" t="s">
-        <v>60</v>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B99" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="102" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B102" s="6" t="s">
-        <v>61</v>
+    <row r="146" spans="2:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" spans="2:7" x14ac:dyDescent="0.15">
+      <c r="B150" s="7" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="146" ht="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" spans="2:7" x14ac:dyDescent="0.15">
+      <c r="G152" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="153" spans="2:7" x14ac:dyDescent="0.15">
+      <c r="G153" t="s">
+        <v>80</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10531,18 +10558,18 @@
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B2" s="2" t="s">
-        <v>62</v>
+      <c r="B2" s="3" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B4" s="2" t="s">
-        <v>63</v>
+      <c r="B4" s="3" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="50" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B50" s="2" t="s">
-        <v>64</v>
+      <c r="B50" s="3" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -10559,13 +10586,13 @@
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B2" s="2" t="s">
-        <v>65</v>
+      <c r="B2" s="3" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B4" s="2" t="s">
-        <v>66</v>
+      <c r="B4" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -10582,12 +10609,12 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B4" s="2" t="s">
-        <v>69</v>
+      <c r="B4" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -10599,22 +10626,22 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91FB7FDE-4389-4DA6-BE1E-C09A313712E8}">
-  <dimension ref="B2:B30"/>
+  <dimension ref="B2:B50"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B2" s="1" t="s">
-        <v>70</v>
+      <c r="B2" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B30" t="s">
-        <v>72</v>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B50" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -10626,32 +10653,42 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B6AD7C9-CDE8-4F75-9F83-73C913947542}">
-  <dimension ref="B2:B118"/>
+  <dimension ref="B2:H162"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B2" s="2" t="s">
-        <v>80</v>
+      <c r="B2" s="3" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B41" t="s">
-        <v>77</v>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B50" t="s">
+        <v>63</v>
       </c>
     </row>
-    <row r="79" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B79" t="s">
-        <v>78</v>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B104" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="118" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B118" t="s">
-        <v>79</v>
+    <row r="159" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B159" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="161" spans="8:8" x14ac:dyDescent="0.15">
+      <c r="H161" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="162" spans="8:8" x14ac:dyDescent="0.15">
+      <c r="H162" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -10663,22 +10700,22 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{925E0D86-D402-473B-B2F7-E46027B2B604}">
-  <dimension ref="B2:B34"/>
+  <dimension ref="B2:B51"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B4" t="s">
+    <row r="2" spans="2:2" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="B2" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B34" t="s">
-        <v>83</v>
+    <row r="4" spans="2:2" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="B4" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B51" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -10699,66 +10736,66 @@
   <sheetData>
     <row r="1" spans="2:40" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="2" spans="2:40" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B2" s="2" t="s">
-        <v>3</v>
+      <c r="B2" s="3" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="2:40" ht="15" x14ac:dyDescent="0.25">
-      <c r="B4" s="3" t="s">
-        <v>15</v>
+      <c r="B4" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -10770,37 +10807,32 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDB1C250-7ABD-4E81-92B5-3B68C1BA5E17}">
-  <dimension ref="B2:G57"/>
+  <dimension ref="B2:M61"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B4" t="s">
-        <v>73</v>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="M6" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="7:7" x14ac:dyDescent="0.15">
       <c r="G23" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B49" s="1" t="s">
+    <row r="61" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B61" s="2" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B51" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B57" t="s">
-        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -10813,32 +10845,22 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C27E20C7-D0B2-4151-B82E-BD4F8F2CA820}">
-  <dimension ref="B2:I88"/>
+  <dimension ref="B2:B56"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B2" s="1" t="s">
-        <v>67</v>
+      <c r="B2" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="9:9" x14ac:dyDescent="0.15">
-      <c r="I20" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B83" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="88" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B88" t="s">
-        <v>20</v>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B56" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -10850,22 +10872,22 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02A7BC2A-B47B-44D9-96C7-5B74F75C82B3}">
-  <dimension ref="B2:B45"/>
+  <dimension ref="B2:B55"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B45" s="2" t="s">
-        <v>23</v>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B55" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -10881,74 +10903,74 @@
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B3" s="3"/>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B4" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B5" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B3" s="2"/>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B4" s="2" t="s">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B6" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B5" s="2" t="s">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B7" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B6" s="2" t="s">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B8" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B7" s="2" t="s">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B9" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B8" s="2" t="s">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B10" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B9" s="2" t="s">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B11" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B10" s="2" t="s">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B12" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B11" s="2" t="s">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B13" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B12" s="2" t="s">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B14" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B13" s="2" t="s">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B15" s="2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B14" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B15" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="M15" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -10960,67 +10982,62 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{260A926D-6497-4D4A-B3E1-0AB8B83F8D79}">
-  <dimension ref="B2:B222"/>
+  <dimension ref="B2:B306"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B5" t="s">
-        <v>47</v>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B4" t="s">
+        <v>70</v>
       </c>
     </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B10" t="s">
-        <v>39</v>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B57" t="s">
+        <v>71</v>
       </c>
     </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B44" t="s">
-        <v>40</v>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B67" t="s">
+        <v>72</v>
       </c>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B51" t="s">
-        <v>41</v>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B121" t="s">
+        <v>75</v>
       </c>
     </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B84" t="s">
-        <v>42</v>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B131" t="s">
+        <v>73</v>
       </c>
     </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B89" t="s">
-        <v>48</v>
+    <row r="185" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B185" t="s">
+        <v>74</v>
       </c>
     </row>
-    <row r="137" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B137" t="s">
-        <v>43</v>
+    <row r="195" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B195" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="142" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B142" t="s">
-        <v>44</v>
+    <row r="243" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B243" t="s">
+        <v>76</v>
       </c>
     </row>
-    <row r="173" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B173" t="s">
-        <v>49</v>
+    <row r="288" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B288" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="200" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B200" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="222" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B222" t="s">
-        <v>46</v>
+    <row r="306" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B306" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -11033,22 +11050,22 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64D94B4F-9DF3-4C0B-912D-B2F2F1D2BC39}">
-  <dimension ref="B2:B37"/>
+  <dimension ref="B2:B55"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B2" s="2" t="s">
-        <v>50</v>
+      <c r="B2" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B37" s="4" t="s">
-        <v>52</v>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B55" s="5" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -11065,12 +11082,12 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.15">
-      <c r="B4" s="2" t="s">
-        <v>54</v>
+      <c r="B4" s="3" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
